--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="105">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,10 +61,13 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -151,42 +157,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Chris Holloway</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
     <t>Eli Brinker</t>
   </si>
   <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>Chris Carbone</t>
-  </si>
-  <si>
-    <t>Chris Holloway</t>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
+    <t>Tomas Angel</t>
   </si>
   <si>
     <t>Shane Leiphart</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Marvin Ta</t>
-  </si>
-  <si>
-    <t>Tomas Angel</t>
+    <t>Joseph Wood</t>
+  </si>
+  <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Colman Closser</t>
   </si>
   <si>
     <t>Michael  Celoni</t>
   </si>
   <si>
-    <t>Colman Closser</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
-    <t>Joseph Wood</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,60 +217,63 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>12.7-1.3-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>12.1-1.8-0.1</t>
+  </si>
+  <si>
+    <t>10.3-3.6-0.2</t>
+  </si>
+  <si>
+    <t>10.3-3.7-0.1</t>
   </si>
   <si>
     <t>8.1-5.8-0.1</t>
   </si>
   <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
+    <t>7.7-6.2-0.2</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.0-0.2</t>
   </si>
   <si>
     <t>6.1-7.8-0.1</t>
   </si>
   <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
+    <t>5.7-8.2-0.1</t>
   </si>
   <si>
     <t>4.3-9.6-0.1</t>
   </si>
   <si>
-    <t>2.1-11.9-0.1</t>
-  </si>
-  <si>
-    <t>13-1</t>
-  </si>
-  <si>
-    <t>9-5</t>
+    <t>3.9-10.0-0.1</t>
+  </si>
+  <si>
+    <t>2.4-11.5-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
+  </si>
+  <si>
+    <t>10-4</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>8-6</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>6-8</t>
   </si>
   <si>
@@ -283,7 +292,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -758,28 +791,28 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3" t="s">
         <v>12</v>
@@ -793,34 +826,34 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
         <v>12</v>
@@ -834,34 +867,34 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -881,28 +914,28 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" t="s">
         <v>12</v>
@@ -925,16 +958,16 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
         <v>12</v>
@@ -954,37 +987,37 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -995,40 +1028,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1045,28 +1078,28 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
         <v>13</v>
@@ -1086,19 +1119,19 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
@@ -1136,10 +1169,10 @@
         <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
         <v>12</v>
@@ -1177,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
@@ -1202,30 +1235,82 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>-10</v>
+      </c>
+      <c r="F3">
+        <v>-4</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1240,13 +1325,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1254,13 +1339,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>0.08333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1268,10 +1353,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.08333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1282,13 +1367,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1296,13 +1381,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1313,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0.4166666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1324,10 +1409,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1341,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1355,10 +1440,10 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>0.5833333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1366,13 +1451,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>0.6666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1380,13 +1465,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>0.8333333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1397,10 +1482,10 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.8333333333333334</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1408,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>0.9166666666666666</v>
+        <v>1.75</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1429,16 +1514,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1446,16 +1531,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1463,16 +1548,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D3">
-        <v>-0.1666666666666666</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1480,16 +1565,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>0.8333333333333334</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D4">
-        <v>0.8333333333333334</v>
+        <v>-0.5833333333333333</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1497,16 +1582,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D5">
-        <v>-0.25</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1514,13 +1599,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>-0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1531,13 +1616,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>-0.4166666666666666</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1551,10 +1636,10 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -1565,16 +1650,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D9">
-        <v>0.3333333333333333</v>
+        <v>-0.08333333333333337</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1582,16 +1667,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D10">
-        <v>-0.75</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1599,13 +1684,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D11">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -1616,16 +1701,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>0.08333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D12">
-        <v>0.08333333333333333</v>
+        <v>-0.5833333333333333</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1633,13 +1718,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -1657,66 +1742,66 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>94.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="C2">
-        <v>4.1</v>
+        <v>25.2</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1745,37 +1830,37 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="D3">
-        <v>22.3</v>
+        <v>41.3</v>
       </c>
       <c r="E3">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="F3">
-        <v>12.1</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1784,51 +1869,51 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>97.3</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0.6</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>17.8</v>
+        <v>32.8</v>
       </c>
       <c r="D4">
-        <v>19.2</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>19.6</v>
+        <v>10.5</v>
       </c>
       <c r="F4">
-        <v>18.1</v>
+        <v>6.3</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J4">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>93.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1836,131 +1921,131 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C5">
-        <v>22.8</v>
+        <v>4.9</v>
       </c>
       <c r="D5">
-        <v>21.5</v>
+        <v>11.4</v>
       </c>
       <c r="E5">
-        <v>17.3</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>13.8</v>
+        <v>19.7</v>
       </c>
       <c r="G5">
-        <v>11.6</v>
+        <v>16.1</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J5">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="L5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N5">
-        <v>93.40000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C6">
-        <v>12.1</v>
+        <v>2.7</v>
       </c>
       <c r="D6">
-        <v>16.5</v>
+        <v>7.9</v>
       </c>
       <c r="E6">
-        <v>17.3</v>
+        <v>21.6</v>
       </c>
       <c r="F6">
-        <v>18.8</v>
+        <v>28.6</v>
       </c>
       <c r="G6">
-        <v>14.4</v>
+        <v>16.4</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="L6">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>89.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>12.4</v>
+        <v>4.2</v>
       </c>
       <c r="E7">
-        <v>15.6</v>
+        <v>11.3</v>
       </c>
       <c r="F7">
-        <v>15.6</v>
+        <v>13.5</v>
       </c>
       <c r="G7">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="H7">
-        <v>13.2</v>
+        <v>18.4</v>
       </c>
       <c r="I7">
-        <v>8.5</v>
+        <v>13.8</v>
       </c>
       <c r="J7">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="K7">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="M7">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="N7">
-        <v>83.59999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1971,221 +2056,221 @@
         <v>0</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.4</v>
+      </c>
+      <c r="E8">
+        <v>3.6</v>
+      </c>
+      <c r="F8">
+        <v>7.7</v>
+      </c>
+      <c r="G8">
+        <v>17.5</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>18.9</v>
+      </c>
+      <c r="J8">
+        <v>18.7</v>
+      </c>
+      <c r="K8">
+        <v>5.9</v>
+      </c>
+      <c r="L8">
+        <v>3.3</v>
+      </c>
+      <c r="M8">
         <v>1</v>
       </c>
-      <c r="D8">
-        <v>2.6</v>
-      </c>
-      <c r="E8">
-        <v>4.4</v>
-      </c>
-      <c r="F8">
-        <v>6.1</v>
-      </c>
-      <c r="G8">
-        <v>11.3</v>
-      </c>
-      <c r="H8">
-        <v>16.4</v>
-      </c>
-      <c r="I8">
-        <v>17.2</v>
-      </c>
-      <c r="J8">
-        <v>17.3</v>
-      </c>
-      <c r="K8">
-        <v>14.7</v>
-      </c>
-      <c r="L8">
-        <v>8.1</v>
-      </c>
-      <c r="M8">
-        <v>0.9</v>
-      </c>
       <c r="N8">
-        <v>41.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D9">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="E9">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="F9">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="G9">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="H9">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="I9">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="J9">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="K9">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="L9">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="N9">
-        <v>41.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E10">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="F10">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G10">
-        <v>8.1</v>
+        <v>12.8</v>
       </c>
       <c r="H10">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="I10">
-        <v>17.4</v>
+        <v>15.6</v>
       </c>
       <c r="J10">
-        <v>18.7</v>
+        <v>14.2</v>
       </c>
       <c r="K10">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="L10">
-        <v>15.7</v>
+        <v>9.5</v>
       </c>
       <c r="M10">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="N10">
-        <v>28</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>11.7</v>
+        <v>4.9</v>
       </c>
       <c r="I11">
-        <v>14.4</v>
+        <v>11.9</v>
       </c>
       <c r="J11">
-        <v>21.7</v>
+        <v>16.2</v>
       </c>
       <c r="K11">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="L11">
-        <v>16.2</v>
+        <v>29.6</v>
       </c>
       <c r="M11">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="N11">
-        <v>21.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0.2</v>
       </c>
-      <c r="D12">
-        <v>0.3</v>
-      </c>
-      <c r="E12">
-        <v>0.9</v>
-      </c>
       <c r="F12">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H12">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="I12">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12">
-        <v>12.7</v>
+        <v>18</v>
       </c>
       <c r="K12">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="L12">
-        <v>36.3</v>
+        <v>28.9</v>
       </c>
       <c r="M12">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="N12">
-        <v>10</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2206,25 +2291,25 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I13">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="L13">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="M13">
-        <v>81.5</v>
+        <v>70.5</v>
       </c>
       <c r="N13">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2234,147 +2319,186 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B2">
+        <v>87.8</v>
+      </c>
+      <c r="C2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>98</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C3">
-        <v>97.39999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D4">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>25.6</v>
+      </c>
+      <c r="C5">
+        <v>86.5</v>
+      </c>
+      <c r="D5">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>94.19999999999999</v>
-      </c>
-      <c r="C4">
-        <v>95.19999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="C5">
-        <v>93.30000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="B6">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="C6">
+        <v>91.10000000000001</v>
+      </c>
+      <c r="D6">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>90.5</v>
-      </c>
-      <c r="C6">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B7">
-        <v>82.5</v>
+        <v>91.10000000000001</v>
       </c>
       <c r="C7">
-        <v>85.90000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>67.2</v>
+      </c>
+      <c r="D7">
+        <v>67.10000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B8">
-        <v>42.4</v>
+        <v>41.6</v>
       </c>
       <c r="C8">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>51.7</v>
+      </c>
+      <c r="D8">
+        <v>52.90000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>0.2</v>
+      </c>
+      <c r="C9">
+        <v>51.2</v>
+      </c>
+      <c r="D9">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>90.7</v>
+      </c>
+      <c r="C10">
+        <v>37.8</v>
+      </c>
+      <c r="D10">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>47.3</v>
-      </c>
-      <c r="C9">
-        <v>40.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>25.6</v>
-      </c>
-      <c r="C10">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="B11">
+        <v>45.9</v>
+      </c>
+      <c r="C11">
+        <v>9.700000000000001</v>
+      </c>
+      <c r="D11">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>21.6</v>
-      </c>
-      <c r="C11">
-        <v>20.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B12">
-        <v>7.3</v>
+        <v>18.6</v>
       </c>
       <c r="C12">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>4.3</v>
+      </c>
+      <c r="D12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B13">
-        <v>0.2</v>
+        <v>7.5</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -2389,28 +2513,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2418,28 +2542,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>112.7</v>
+        <v>103.2</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>127.69</v>
+        <v>118.68</v>
       </c>
       <c r="G2">
-        <v>0.615</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2447,28 +2571,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>131.1</v>
+        <v>90.98</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>125.33</v>
+        <v>118.93</v>
       </c>
       <c r="G3">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2476,28 +2600,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>77.81999999999999</v>
+        <v>116.5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>124</v>
+        <v>119.72</v>
       </c>
       <c r="G4">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H4">
         <v>0.8</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2505,28 +2629,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>108.72</v>
+        <v>106.87</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>122.33</v>
+        <v>118.15</v>
       </c>
       <c r="G5">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2534,28 +2658,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>136.96</v>
+        <v>109.18</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>121.06</v>
+        <v>119.63</v>
       </c>
       <c r="G6">
-        <v>0.385</v>
+        <v>0.583</v>
       </c>
       <c r="H6">
         <v>0.5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2563,28 +2687,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>101</v>
+        <v>127.88</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>121.14</v>
+        <v>116.45</v>
       </c>
       <c r="G7">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H7">
         <v>0.1</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2592,28 +2716,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>124.66</v>
+        <v>118.47</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>121.72</v>
+        <v>118.02</v>
       </c>
       <c r="G8">
-        <v>0.462</v>
+        <v>0.583</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2621,28 +2745,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>115.66</v>
+        <v>137.87</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>121.5</v>
+        <v>114.85</v>
       </c>
       <c r="G9">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
       <c r="H9">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2650,28 +2774,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>110.16</v>
+        <v>117.79</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>121.12</v>
+        <v>116.33</v>
       </c>
       <c r="G10">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2679,28 +2803,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>137.66</v>
+        <v>146.24</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>120.05</v>
+        <v>114.76</v>
       </c>
       <c r="G11">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H11">
         <v>-0.8</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2708,28 +2832,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12">
-        <v>175.36</v>
+        <v>111.32</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>117.6</v>
+        <v>115.54</v>
       </c>
       <c r="G12">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2737,28 +2861,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13">
-        <v>128.52</v>
+        <v>120.54</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>116.8</v>
+        <v>115.79</v>
       </c>
       <c r="G13">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2773,48 +2897,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>175.36</v>
+        <v>137.87</v>
       </c>
       <c r="E2">
-        <v>175.36</v>
+        <v>275.74</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2823,68 +2947,68 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>136.96</v>
+        <v>127.88</v>
       </c>
       <c r="E3">
-        <v>136.96</v>
+        <v>255.76</v>
       </c>
       <c r="F3">
-        <v>97.3</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>137.66</v>
+        <v>146.24</v>
       </c>
       <c r="E4">
-        <v>137.66</v>
+        <v>292.48</v>
       </c>
       <c r="F4">
-        <v>93.8</v>
+        <v>99.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2892,86 +3016,86 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>128.52</v>
+        <v>117.79</v>
       </c>
       <c r="E5">
-        <v>128.52</v>
+        <v>235.58</v>
       </c>
       <c r="F5">
-        <v>93.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>131.1</v>
+        <v>120.54</v>
       </c>
       <c r="E6">
-        <v>131.1</v>
+        <v>241.08</v>
       </c>
       <c r="F6">
-        <v>89.5</v>
+        <v>86.5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>124.66</v>
+        <v>116.5</v>
       </c>
       <c r="E7">
-        <v>124.66</v>
+        <v>233</v>
       </c>
       <c r="F7">
-        <v>83.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2979,173 +3103,173 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>115.66</v>
+        <v>118.47</v>
       </c>
       <c r="E8">
-        <v>115.66</v>
+        <v>236.94</v>
       </c>
       <c r="F8">
-        <v>41.8</v>
+        <v>52.2</v>
       </c>
       <c r="G8">
-        <v>0.8999999999999999</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>108.72</v>
+        <v>106.87</v>
       </c>
       <c r="E9">
-        <v>108.72</v>
+        <v>213.74</v>
       </c>
       <c r="F9">
-        <v>41.09999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="G9">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>110.16</v>
+        <v>111.32</v>
       </c>
       <c r="E10">
-        <v>110.16</v>
+        <v>222.64</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>43.7</v>
       </c>
       <c r="G10">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>112.7</v>
+        <v>103.2</v>
       </c>
       <c r="E11">
-        <v>112.7</v>
+        <v>206.4</v>
       </c>
       <c r="F11">
-        <v>21.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G11">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>101</v>
+        <v>109.18</v>
       </c>
       <c r="E12">
-        <v>101</v>
+        <v>218.36</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="G12">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>77.81999999999999</v>
+        <v>90.97999999999999</v>
       </c>
       <c r="E13">
-        <v>77.81999999999999</v>
+        <v>181.96</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G13">
-        <v>81.5</v>
+        <v>70.5</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3284,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3183,16 +3307,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3203,7 +3327,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -3211,8 +3335,8 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3220,19 +3344,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="F4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3240,19 +3364,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3260,19 +3384,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>49</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3280,19 +3404,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3300,19 +3424,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3320,19 +3444,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3343,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3363,16 +3487,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D11">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3380,19 +3504,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12">
-        <v>0</v>
+      <c r="F12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3400,19 +3524,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
       <c r="D13">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3422,18 +3546,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -3441,10 +3568,13 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3452,76 +3582,97 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>-1</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3529,10 +3680,13 @@
         <v>-2</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>-4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -3540,29 +3694,38 @@
         <v>-2</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>-4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>-10</v>
+      </c>
+      <c r="C12">
+        <v>-10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>-8</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13">
-        <v>-10</v>
-      </c>
       <c r="C13">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="106">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -226,34 +226,34 @@
     <t>0-2</t>
   </si>
   <si>
+    <t>10.2-3.6-0.2</t>
+  </si>
+  <si>
     <t>12.1-1.8-0.1</t>
   </si>
   <si>
-    <t>10.3-3.6-0.2</t>
-  </si>
-  <si>
-    <t>10.3-3.7-0.1</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.2</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.0-0.2</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>4.3-9.6-0.1</t>
+    <t>10.3-3.6-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.2</t>
+  </si>
+  <si>
+    <t>6.2-7.8-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
+  </si>
+  <si>
+    <t>4.3-9.5-0.1</t>
   </si>
   <si>
     <t>3.9-10.0-0.1</t>
@@ -262,19 +262,22 @@
     <t>2.4-11.5-0.1</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
-    <t>11-3</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
+  </si>
+  <si>
+    <t>5-9</t>
   </si>
   <si>
     <t>4-10</t>
@@ -1240,25 +1243,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1786,28 +1789,28 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>69.3</v>
+        <v>7.1</v>
       </c>
       <c r="C2">
-        <v>25.2</v>
+        <v>31.9</v>
       </c>
       <c r="D2">
-        <v>4.7</v>
+        <v>42.7</v>
       </c>
       <c r="E2">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="F2">
+        <v>4.3</v>
+      </c>
+      <c r="G2">
+        <v>1.4</v>
+      </c>
+      <c r="H2">
         <v>0.2</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1830,31 +1833,31 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C3">
-        <v>32.3</v>
+        <v>24.6</v>
       </c>
       <c r="D3">
-        <v>41.3</v>
+        <v>5.2</v>
       </c>
       <c r="E3">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="F3">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1869,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1877,34 +1880,34 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>22.8</v>
       </c>
       <c r="C4">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="E4">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
       <c r="F4">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="G4">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
         <v>0.2</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1913,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1921,43 +1924,43 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="C5">
         <v>4.9</v>
       </c>
       <c r="D5">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="F5">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="G5">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="L5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M5">
         <v>0.1</v>
       </c>
       <c r="N5">
-        <v>88.7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1968,31 +1971,31 @@
         <v>0.3</v>
       </c>
       <c r="C6">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="D6">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="E6">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="F6">
-        <v>28.6</v>
+        <v>23.7</v>
       </c>
       <c r="G6">
-        <v>16.4</v>
+        <v>17.3</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="K6">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="L6">
         <v>0.5</v>
@@ -2001,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2009,43 +2012,43 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D7">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="E7">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="G7">
-        <v>19.6</v>
+        <v>16.8</v>
       </c>
       <c r="H7">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="I7">
-        <v>13.8</v>
+        <v>15.4</v>
       </c>
       <c r="J7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M7">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N7">
-        <v>68</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2056,40 +2059,40 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="G8">
         <v>17.5</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>21.1</v>
       </c>
       <c r="I8">
-        <v>18.9</v>
+        <v>20.8</v>
       </c>
       <c r="J8">
-        <v>18.7</v>
+        <v>16.5</v>
       </c>
       <c r="K8">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="L8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N8">
-        <v>52.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2103,37 +2106,37 @@
         <v>0.9</v>
       </c>
       <c r="D9">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="E9">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="F9">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="G9">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="H9">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="I9">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="J9">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="K9">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="L9">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M9">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="N9">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2141,43 +2144,43 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0.2</v>
       </c>
       <c r="D10">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G10">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="H10">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="I10">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="J10">
-        <v>14.2</v>
+        <v>15.1</v>
       </c>
       <c r="K10">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="L10">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="M10">
         <v>4.2</v>
       </c>
       <c r="N10">
-        <v>43.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2191,37 +2194,37 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H11">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>11.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11">
-        <v>16.2</v>
+        <v>18.5</v>
       </c>
       <c r="K11">
-        <v>25.6</v>
+        <v>24.9</v>
       </c>
       <c r="L11">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="M11">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N11">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2238,34 +2241,34 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H12">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>15.1</v>
       </c>
       <c r="K12">
-        <v>24.6</v>
+        <v>29.1</v>
       </c>
       <c r="L12">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="M12">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="N12">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2288,28 +2291,28 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="K13">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="L13">
-        <v>18.8</v>
+        <v>17.1</v>
       </c>
       <c r="M13">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="N13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2335,13 +2338,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>87.8</v>
+        <v>98.2</v>
       </c>
       <c r="C2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2349,16 +2352,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>97.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2369,38 +2372,38 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="D4">
-        <v>99.7</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>25.6</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="C5">
-        <v>86.5</v>
+        <v>91</v>
       </c>
       <c r="D5">
-        <v>89.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>93.40000000000001</v>
+        <v>25.7</v>
       </c>
       <c r="C6">
-        <v>91.10000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D6">
-        <v>88.3</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2408,13 +2411,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>91.10000000000001</v>
+        <v>90.10000000000001</v>
       </c>
       <c r="C7">
-        <v>67.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="D7">
-        <v>67.10000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2422,13 +2425,13 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="C8">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="D8">
-        <v>52.90000000000001</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2439,10 +2442,10 @@
         <v>0.2</v>
       </c>
       <c r="C9">
-        <v>51.2</v>
+        <v>49.5</v>
       </c>
       <c r="D9">
-        <v>45.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2450,41 +2453,41 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>90.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C10">
-        <v>37.8</v>
+        <v>40.6</v>
       </c>
       <c r="D10">
-        <v>41.8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>45.9</v>
+        <v>18.9</v>
       </c>
       <c r="C11">
-        <v>9.700000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="D11">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>18.6</v>
+        <v>48.2</v>
       </c>
       <c r="C12">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D12">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2495,10 +2498,10 @@
         <v>7.5</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>0.4</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2929,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -2935,10 +2938,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>137.87</v>
+        <v>127.88</v>
       </c>
       <c r="E2">
-        <v>275.74</v>
+        <v>255.76</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2955,7 +2958,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -2964,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>127.88</v>
+        <v>137.87</v>
       </c>
       <c r="E3">
-        <v>255.76</v>
+        <v>275.74</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2999,7 +3002,7 @@
         <v>292.48</v>
       </c>
       <c r="F4">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3008,7 +3011,7 @@
         <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3028,7 +3031,7 @@
         <v>235.58</v>
       </c>
       <c r="F5">
-        <v>88.7</v>
+        <v>89</v>
       </c>
       <c r="G5">
         <v>0.1</v>
@@ -3037,7 +3040,7 @@
         <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3057,7 +3060,7 @@
         <v>241.08</v>
       </c>
       <c r="F6">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3066,7 +3069,7 @@
         <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3086,16 +3089,16 @@
         <v>233</v>
       </c>
       <c r="F7">
-        <v>68</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="G7">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="s">
         <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3115,10 +3118,10 @@
         <v>236.94</v>
       </c>
       <c r="F8">
-        <v>52.2</v>
+        <v>50.4</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H8" t="s">
         <v>73</v>
@@ -3144,10 +3147,10 @@
         <v>213.74</v>
       </c>
       <c r="F9">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="s">
         <v>74</v>
@@ -3173,7 +3176,7 @@
         <v>222.64</v>
       </c>
       <c r="F10">
-        <v>43.7</v>
+        <v>42</v>
       </c>
       <c r="G10">
         <v>4.2</v>
@@ -3182,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3202,16 +3205,16 @@
         <v>206.4</v>
       </c>
       <c r="F11">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H11" t="s">
         <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3231,16 +3234,16 @@
         <v>218.36</v>
       </c>
       <c r="F12">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="G12">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="H12" t="s">
         <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3260,16 +3263,16 @@
         <v>181.96</v>
       </c>
       <c r="F13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G13">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="H13" t="s">
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3287,16 +3290,16 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3316,7 +3319,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3336,7 +3339,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3356,7 +3359,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3376,7 +3379,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3396,7 +3399,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3416,7 +3419,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3436,7 +3439,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3456,7 +3459,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3476,7 +3479,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3496,7 +3499,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3516,7 +3519,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3536,7 +3539,7 @@
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3551,13 +3554,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3571,7 +3574,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3585,7 +3588,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3599,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3613,7 +3616,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3627,7 +3630,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3641,7 +3644,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3655,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3669,7 +3672,7 @@
         <v>-1</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3683,7 +3686,7 @@
         <v>-4</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3697,7 +3700,7 @@
         <v>-4</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3711,7 +3714,7 @@
         <v>-10</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3725,7 +3728,7 @@
         <v>-13</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="116">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,13 +61,16 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -160,39 +166,39 @@
     <t>Chris Holloway</t>
   </si>
   <si>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
+    <t>Joseph Wood</t>
+  </si>
+  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
+    <t>Tomas Angel</t>
+  </si>
+  <si>
+    <t>Michael  Celoni</t>
+  </si>
+  <si>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Chris Carbone</t>
-  </si>
-  <si>
     <t>Eli Brinker</t>
   </si>
   <si>
-    <t>Marvin Ta</t>
-  </si>
-  <si>
-    <t>Tomas Angel</t>
-  </si>
-  <si>
     <t>Shane Leiphart</t>
   </si>
   <si>
-    <t>Joseph Wood</t>
-  </si>
-  <si>
     <t>Robbie Wilston</t>
   </si>
   <si>
     <t>Colman Closser</t>
   </si>
   <si>
-    <t>Michael  Celoni</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -217,55 +223,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>10.2-3.6-0.2</t>
-  </si>
-  <si>
-    <t>12.1-1.8-0.1</t>
-  </si>
-  <si>
-    <t>10.3-3.6-0.1</t>
-  </si>
-  <si>
-    <t>8.1-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.2</t>
-  </si>
-  <si>
-    <t>6.2-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.0-2.9-0.1</t>
+  </si>
+  <si>
+    <t>10.1-3.8-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.1-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
   </si>
   <si>
     <t>4.3-9.5-0.1</t>
   </si>
   <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>2.4-11.5-0.1</t>
+    <t>3.6-10.3-0.1</t>
+  </si>
+  <si>
+    <t>3.1-10.8-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>12-2</t>
+    <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
@@ -283,7 +295,7 @@
     <t>4-10</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -295,31 +307,49 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑5</t>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑11</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓6</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -747,22 +777,22 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -774,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -791,22 +821,22 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -815,7 +845,7 @@
         <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
         <v>12</v>
@@ -829,25 +859,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
@@ -870,10 +900,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -888,16 +918,16 @@
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -914,22 +944,22 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
         <v>13</v>
@@ -938,7 +968,7 @@
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
         <v>12</v>
@@ -949,40 +979,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
         <v>13</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -996,19 +1026,19 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1052,19 +1082,19 @@
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" t="s">
         <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1078,10 +1108,10 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -1093,16 +1123,16 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" t="s">
         <v>13</v>
@@ -1113,22 +1143,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1137,16 +1167,16 @@
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1172,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
         <v>12</v>
@@ -1195,22 +1225,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -1225,10 +1255,10 @@
         <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1238,30 +1268,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1269,25 +1299,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1295,25 +1325,103 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>0</v>
       </c>
       <c r="E3">
         <v>-10</v>
       </c>
       <c r="F3">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>-10</v>
+      </c>
+      <c r="F5">
+        <v>-4</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1328,13 +1436,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1345,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1359,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.4166666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1370,13 +1478,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1384,13 +1492,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1401,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1412,13 +1520,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0.9166666666666666</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1426,13 +1534,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1440,13 +1548,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1454,10 +1562,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>1.25</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1471,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1482,13 +1590,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>1.666666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1499,10 +1607,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>1.75</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1517,16 +1625,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1537,13 +1645,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1.833333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D2">
-        <v>-0.1666666666666667</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1551,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1.583333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.4166666666666667</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -1568,16 +1676,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.416666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.5833333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1585,16 +1693,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>1.166666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D5">
-        <v>-0.8333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1602,13 +1710,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1619,13 +1727,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1636,16 +1744,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1653,16 +1761,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.9166666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D9">
-        <v>-0.08333333333333337</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1670,16 +1778,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>0.9166666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D10">
-        <v>0.9166666666666666</v>
+        <v>-0.75</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1687,16 +1795,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>0.6666666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D11">
-        <v>0.6666666666666666</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1704,16 +1812,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.4166666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D12">
-        <v>-0.5833333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1721,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>0.08333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D13">
-        <v>0.08333333333333333</v>
+        <v>-0.5833333333333333</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1745,72 +1853,72 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>7.1</v>
+        <v>63.1</v>
       </c>
       <c r="C2">
-        <v>31.9</v>
+        <v>21.7</v>
       </c>
       <c r="D2">
-        <v>42.7</v>
+        <v>9.6</v>
       </c>
       <c r="E2">
-        <v>12.4</v>
+        <v>3.4</v>
       </c>
       <c r="F2">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="G2">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1833,31 +1941,31 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>69.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>24.6</v>
+        <v>32.8</v>
       </c>
       <c r="D3">
-        <v>5.2</v>
+        <v>23.4</v>
       </c>
       <c r="E3">
-        <v>0.9</v>
+        <v>11.3</v>
       </c>
       <c r="F3">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1872,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1880,87 +1988,87 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>22.8</v>
+        <v>7.4</v>
       </c>
       <c r="C4">
-        <v>32.9</v>
+        <v>18.9</v>
       </c>
       <c r="D4">
-        <v>23.4</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="F4">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>11.8</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0.3</v>
+      </c>
+      <c r="L4">
         <v>0.2</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>99.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="C5">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="D5">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="E5">
-        <v>27.2</v>
+        <v>19.7</v>
       </c>
       <c r="F5">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="G5">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>89</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1968,224 +2076,224 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>8.6</v>
       </c>
       <c r="D6">
-        <v>9.5</v>
+        <v>12.7</v>
       </c>
       <c r="E6">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="F6">
-        <v>23.7</v>
+        <v>19.2</v>
       </c>
       <c r="G6">
-        <v>17.3</v>
+        <v>14.9</v>
       </c>
       <c r="H6">
         <v>11.2</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J6">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="L6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>86.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>0.2</v>
-      </c>
-      <c r="C7">
-        <v>2.1</v>
-      </c>
       <c r="D7">
-        <v>3.2</v>
+        <v>9.1</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="F7">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="G7">
-        <v>16.8</v>
+        <v>18.4</v>
       </c>
       <c r="H7">
-        <v>17.6</v>
+        <v>16.4</v>
       </c>
       <c r="I7">
-        <v>15.4</v>
+        <v>10.2</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="L7">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>67.3</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F8">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="G8">
-        <v>17.5</v>
+        <v>20.4</v>
       </c>
       <c r="H8">
-        <v>21.1</v>
+        <v>23</v>
       </c>
       <c r="I8">
-        <v>20.8</v>
+        <v>15.8</v>
       </c>
       <c r="J8">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="K8">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="N8">
-        <v>50.4</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
-        <v>11.3</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="H9">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="I9">
-        <v>16.1</v>
+        <v>22.1</v>
       </c>
       <c r="J9">
-        <v>15.4</v>
+        <v>22.6</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="L9">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="M9">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="N9">
-        <v>48.5</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
+        <v>1.3</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>5.9</v>
+      </c>
+      <c r="H10">
+        <v>9.5</v>
+      </c>
+      <c r="I10">
+        <v>17.5</v>
+      </c>
+      <c r="J10">
+        <v>23.8</v>
+      </c>
+      <c r="K10">
+        <v>18.4</v>
+      </c>
+      <c r="L10">
+        <v>15</v>
+      </c>
+      <c r="M10">
         <v>5</v>
       </c>
-      <c r="F10">
-        <v>7.9</v>
-      </c>
-      <c r="G10">
-        <v>13.8</v>
-      </c>
-      <c r="H10">
-        <v>14.1</v>
-      </c>
-      <c r="I10">
-        <v>15.3</v>
-      </c>
-      <c r="J10">
-        <v>15.1</v>
-      </c>
-      <c r="K10">
-        <v>12</v>
-      </c>
-      <c r="L10">
-        <v>11.4</v>
-      </c>
-      <c r="M10">
-        <v>4.2</v>
-      </c>
       <c r="N10">
-        <v>42</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2194,48 +2302,48 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I11">
-        <v>9.199999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="J11">
-        <v>18.5</v>
+        <v>22.1</v>
       </c>
       <c r="K11">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="L11">
-        <v>28.7</v>
+        <v>18.1</v>
       </c>
       <c r="M11">
-        <v>8.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="N11">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2244,36 +2352,36 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>15.1</v>
+        <v>11.2</v>
       </c>
       <c r="K12">
-        <v>29.1</v>
+        <v>21.6</v>
       </c>
       <c r="L12">
-        <v>29.3</v>
+        <v>31.4</v>
       </c>
       <c r="M12">
-        <v>11.2</v>
+        <v>25.3</v>
       </c>
       <c r="N12">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2294,25 +2402,25 @@
         <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J13">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
-        <v>6.3</v>
+        <v>13.2</v>
       </c>
       <c r="L13">
-        <v>17.1</v>
+        <v>25</v>
       </c>
       <c r="M13">
-        <v>72.8</v>
+        <v>55.1</v>
       </c>
       <c r="N13">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2322,26 +2430,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>98.2</v>
+        <v>99.2</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2349,22 +2460,28 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>83.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C3">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>99.3</v>
+      </c>
+      <c r="E3">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -2372,135 +2489,165 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>99.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="E4">
+        <v>96.39999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>95.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="C5">
-        <v>91</v>
+        <v>62.7</v>
       </c>
       <c r="D5">
-        <v>88.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E5">
+        <v>93.60000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B6">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>87.5</v>
+        <v>90.2</v>
       </c>
       <c r="D6">
-        <v>86.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="E6">
+        <v>92.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>90.10000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="C7">
-        <v>65.60000000000001</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>78.10000000000001</v>
+      </c>
+      <c r="E7">
+        <v>83.89999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>94.69999999999999</v>
+      </c>
+      <c r="C8">
+        <v>32.8</v>
+      </c>
+      <c r="D8">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E8">
+        <v>68.10000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>97.89999999999999</v>
+      </c>
+      <c r="C9">
+        <v>94.69999999999999</v>
+      </c>
+      <c r="D9">
+        <v>33.90000000000001</v>
+      </c>
+      <c r="E9">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
+        <v>38.2</v>
+      </c>
+      <c r="D10">
+        <v>23.2</v>
+      </c>
+      <c r="E10">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>41.5</v>
-      </c>
-      <c r="C8">
-        <v>50.8</v>
-      </c>
-      <c r="D8">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>0.2</v>
-      </c>
-      <c r="C9">
-        <v>49.5</v>
-      </c>
-      <c r="D9">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="C10">
-        <v>40.6</v>
-      </c>
-      <c r="D10">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B11">
-        <v>18.9</v>
+        <v>36.5</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>58.7</v>
       </c>
       <c r="D11">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>7.9</v>
+      </c>
+      <c r="E11">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>3.8</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
+        <v>3.5</v>
+      </c>
+      <c r="E12">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>48.2</v>
-      </c>
-      <c r="C12">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="D12">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B13">
-        <v>7.5</v>
+        <v>45</v>
       </c>
       <c r="C13">
-        <v>0.2</v>
+        <v>11.9</v>
       </c>
       <c r="D13">
+        <v>0.4</v>
+      </c>
+      <c r="E13">
         <v>0.8999999999999999</v>
       </c>
     </row>
@@ -2516,28 +2663,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2548,25 +2695,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>103.2</v>
+        <v>92.05</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>118.68</v>
+        <v>119.6</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2574,28 +2721,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>90.98</v>
+        <v>102.4</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>118.93</v>
+        <v>118.66</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2603,28 +2750,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>116.5</v>
+        <v>105.9</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>119.72</v>
+        <v>118.34</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.485</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2632,28 +2779,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>106.87</v>
+        <v>104.15</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>118.15</v>
+        <v>118.5</v>
       </c>
       <c r="G5">
-        <v>0.542</v>
+        <v>0.545</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2661,28 +2808,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>109.18</v>
+        <v>110.47</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>119.63</v>
+        <v>117.93</v>
       </c>
       <c r="G6">
-        <v>0.583</v>
+        <v>0.545</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2690,28 +2837,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>127.88</v>
+        <v>123.61</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>116.45</v>
+        <v>116.73</v>
       </c>
       <c r="G7">
-        <v>0.417</v>
+        <v>0.485</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2719,28 +2866,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>118.47</v>
+        <v>127.8</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>118.02</v>
+        <v>116.35</v>
       </c>
       <c r="G8">
-        <v>0.583</v>
+        <v>0.455</v>
       </c>
       <c r="H8">
         <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2748,28 +2895,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>137.87</v>
+        <v>124.55</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>114.85</v>
+        <v>116.65</v>
       </c>
       <c r="G9">
-        <v>0.417</v>
+        <v>0.485</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2777,28 +2924,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>117.79</v>
+        <v>125.67</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>116.33</v>
+        <v>116.55</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.515</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2806,28 +2953,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>146.24</v>
+        <v>141.93</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>114.76</v>
+        <v>115.07</v>
       </c>
       <c r="G11">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H11">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2835,28 +2982,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12">
+        <v>128.72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>116.27</v>
+      </c>
+      <c r="G12">
+        <v>0.485</v>
+      </c>
+      <c r="H12">
+        <v>-1</v>
+      </c>
+      <c r="I12">
         <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12">
-        <v>111.32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12">
-        <v>115.54</v>
-      </c>
-      <c r="G12">
-        <v>0.5</v>
-      </c>
-      <c r="H12">
-        <v>-1.1</v>
-      </c>
-      <c r="I12">
-        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2864,28 +3011,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13">
-        <v>120.54</v>
+        <v>120.43</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>115.79</v>
+        <v>117.02</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H13">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2900,48 +3047,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>127.88</v>
+        <v>141.9266666666666</v>
       </c>
       <c r="E2">
-        <v>255.76</v>
+        <v>425.78</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2950,39 +3097,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>137.87</v>
+        <v>127.8</v>
       </c>
       <c r="E3">
-        <v>275.74</v>
+        <v>383.4</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2990,57 +3137,57 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>146.24</v>
+        <v>128.72</v>
       </c>
       <c r="E4">
-        <v>292.48</v>
+        <v>386.16</v>
       </c>
       <c r="F4">
-        <v>99.09999999999999</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>117.79</v>
+        <v>124.5466666666667</v>
       </c>
       <c r="E5">
-        <v>235.58</v>
+        <v>373.64</v>
       </c>
       <c r="F5">
-        <v>89</v>
+        <v>94.8</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3048,231 +3195,231 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>120.54</v>
+        <v>123.6133333333333</v>
       </c>
       <c r="E6">
-        <v>241.08</v>
+        <v>370.84</v>
       </c>
       <c r="F6">
-        <v>86.59999999999999</v>
+        <v>93.10000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>116.5</v>
+        <v>125.6666666666667</v>
       </c>
       <c r="E7">
-        <v>233</v>
+        <v>377</v>
       </c>
       <c r="F7">
-        <v>67.30000000000001</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="G7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>118.47</v>
+        <v>120.4266666666667</v>
       </c>
       <c r="E8">
-        <v>236.94</v>
+        <v>361.28</v>
       </c>
       <c r="F8">
-        <v>50.4</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="G8">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D9">
-        <v>106.87</v>
+        <v>105.9</v>
       </c>
       <c r="E9">
-        <v>213.74</v>
+        <v>317.7</v>
       </c>
       <c r="F9">
-        <v>48.5</v>
+        <v>29.7</v>
       </c>
       <c r="G9">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D10">
-        <v>111.32</v>
+        <v>102.4</v>
       </c>
       <c r="E10">
-        <v>222.64</v>
+        <v>307.2</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>20.3</v>
       </c>
       <c r="G10">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>103.2</v>
+        <v>110.4733333333333</v>
       </c>
       <c r="E11">
-        <v>206.4</v>
+        <v>331.42</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G11">
-        <v>8.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>109.18</v>
+        <v>104.1466666666666</v>
       </c>
       <c r="E12">
-        <v>218.36</v>
+        <v>312.4399999999999</v>
       </c>
       <c r="F12">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="G12">
-        <v>11.2</v>
+        <v>25.3</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13">
-        <v>90.97999999999999</v>
+        <v>92.04666666666667</v>
       </c>
       <c r="E13">
-        <v>181.96</v>
+        <v>276.14</v>
       </c>
       <c r="F13">
-        <v>0.6</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G13">
-        <v>72.8</v>
+        <v>55.1</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3287,19 +3434,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3307,19 +3454,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3327,19 +3474,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3347,19 +3494,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3367,19 +3514,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3387,19 +3534,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3407,19 +3554,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3427,19 +3574,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3447,19 +3594,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3470,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3487,19 +3634,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3513,13 +3660,13 @@
         <v>47</v>
       </c>
       <c r="D12">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3530,16 +3677,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3549,93 +3696,111 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>-2</v>
+      </c>
+      <c r="C5">
+        <v>-4</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>-1</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3643,39 +3808,48 @@
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B8">
+        <v>-1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>-1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3685,25 +3859,31 @@
       <c r="C10">
         <v>-4</v>
       </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>-4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>-1</v>
+      </c>
+      <c r="D11">
+        <v>-10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -3713,11 +3893,14 @@
       <c r="C12">
         <v>-10</v>
       </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12">
+        <v>-17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3727,8 +3910,11 @@
       <c r="C13">
         <v>-13</v>
       </c>
-      <c r="D13" t="s">
-        <v>96</v>
+      <c r="D13">
+        <v>-19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="117">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,16 +61,19 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,42 +169,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
     <t>Chris Holloway</t>
   </si>
   <si>
+    <t>Michael  Celoni</t>
+  </si>
+  <si>
+    <t>Joseph Wood</t>
+  </si>
+  <si>
     <t>Chris Carbone</t>
   </si>
   <si>
-    <t>Joseph Wood</t>
+    <t>Colman Closser</t>
+  </si>
+  <si>
+    <t>Tomas Angel</t>
+  </si>
+  <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
+    <t>Shane Leiphart</t>
   </si>
   <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Tomas Angel</t>
-  </si>
-  <si>
-    <t>Michael  Celoni</t>
-  </si>
-  <si>
-    <t>Marvin Ta</t>
-  </si>
-  <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
     <t>Eli Brinker</t>
   </si>
   <si>
-    <t>Shane Leiphart</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
-    <t>Colman Closser</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,58 +229,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>11.0-2.9-0.1</t>
-  </si>
-  <si>
-    <t>10.1-3.8-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.5-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.1-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>10.9-3.0-0.1</t>
+  </si>
+  <si>
+    <t>10.3-3.6-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.6-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.6-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
   </si>
   <si>
     <t>5.4-8.5-0.1</t>
   </si>
   <si>
-    <t>4.3-9.5-0.1</t>
-  </si>
-  <si>
-    <t>3.6-10.3-0.1</t>
-  </si>
-  <si>
-    <t>3.1-10.8-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>3.2-10.8-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>9-5</t>
@@ -292,9 +298,6 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
     <t>3-11</t>
   </si>
   <si>
@@ -307,40 +310,37 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑5</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↑11</t>
+    <t>↓8</t>
   </si>
   <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↑1</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -777,22 +780,22 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -804,7 +807,7 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -815,40 +818,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -856,40 +859,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s">
         <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -906,22 +909,22 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>15</v>
@@ -938,40 +941,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" t="s">
         <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -979,40 +982,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1020,37 +1023,37 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -1061,25 +1064,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1088,13 +1091,13 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1102,25 +1105,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -1129,13 +1132,13 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1143,13 +1146,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -1161,22 +1164,22 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1184,40 +1187,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
         <v>12</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" t="s">
         <v>13</v>
-      </c>
-      <c r="M12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1225,40 +1228,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1268,30 +1271,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1299,25 +1302,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>-17</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1325,25 +1328,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
       <c r="E3">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1351,25 +1354,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1377,22 +1380,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>0</v>
       </c>
       <c r="E5">
         <v>-10</v>
       </c>
       <c r="F5">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
         <v>6</v>
@@ -1403,24 +1406,102 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>-10</v>
+      </c>
+      <c r="F7">
+        <v>-4</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
+      <c r="E9">
         <v>11</v>
       </c>
-      <c r="F6">
+      <c r="F9">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1436,13 +1517,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1453,10 +1534,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1467,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1478,13 +1559,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>0.9166666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1492,13 +1573,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>1.083333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1509,10 +1590,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1523,10 +1604,10 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>1.583333333333333</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1537,10 +1618,10 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>1.583333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1548,13 +1629,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>1.75</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1562,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1.833333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1576,13 +1657,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1593,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>2.083333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1607,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>2.583333333333333</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1625,16 +1706,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1645,10 +1726,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2.666666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="D2">
-        <v>0.6666666666666665</v>
+        <v>0.25</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -1662,13 +1743,13 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>1.916666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D3">
         <v>-1.083333333333333</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1676,16 +1757,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1.833333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.1666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1696,10 +1777,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1.833333333333333</v>
+        <v>2.25</v>
       </c>
       <c r="D5">
-        <v>-0.1666666666666667</v>
+        <v>-0.75</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1710,16 +1791,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1.666666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D6">
-        <v>0.6666666666666667</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1727,16 +1808,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0.6666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1747,13 +1828,13 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>1.583333333333333</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>-0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1761,16 +1842,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>1.333333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D9">
-        <v>1.333333333333333</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1778,16 +1859,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="D10">
-        <v>-0.75</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1795,16 +1876,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1.166666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D11">
-        <v>-0.8333333333333333</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1812,16 +1893,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.6666666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D12">
-        <v>0.6666666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1832,13 +1913,13 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D13">
-        <v>-0.5833333333333333</v>
+        <v>-0.4166666666666666</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1853,81 +1934,81 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>63.1</v>
+        <v>54.5</v>
       </c>
       <c r="C2">
-        <v>21.7</v>
+        <v>30.5</v>
       </c>
       <c r="D2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="E2">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="F2">
         <v>1.8</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
+        <v>0.2</v>
+      </c>
+      <c r="I2">
         <v>0.1</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1936,36 +2017,36 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>19.7</v>
+        <v>37.1</v>
       </c>
       <c r="C3">
-        <v>32.8</v>
+        <v>39.3</v>
       </c>
       <c r="D3">
-        <v>23.4</v>
+        <v>13.2</v>
       </c>
       <c r="E3">
-        <v>11.3</v>
+        <v>6.4</v>
       </c>
       <c r="F3">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1980,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1988,34 +2069,34 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="C4">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>24.9</v>
       </c>
       <c r="E4">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="F4">
-        <v>15.6</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="L4">
         <v>0.2</v>
@@ -2024,51 +2105,51 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>96.90000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="C5">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>18.8</v>
+        <v>16.3</v>
       </c>
       <c r="E5">
-        <v>19.7</v>
+        <v>17.5</v>
       </c>
       <c r="F5">
-        <v>19.5</v>
+        <v>14.4</v>
       </c>
       <c r="G5">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="L5">
         <v>0.3</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N5">
-        <v>94.8</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2076,312 +2157,312 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="C6">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>12.7</v>
+        <v>9.6</v>
       </c>
       <c r="E6">
-        <v>21.9</v>
+        <v>15.5</v>
       </c>
       <c r="F6">
-        <v>19.2</v>
+        <v>16.2</v>
       </c>
       <c r="G6">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>11.2</v>
+        <v>13.7</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>12.6</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="L6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6">
-        <v>93.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D7">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>14.2</v>
+        <v>11.2</v>
       </c>
       <c r="F7">
-        <v>17.7</v>
+        <v>15.1</v>
       </c>
       <c r="G7">
-        <v>18.4</v>
+        <v>13.8</v>
       </c>
       <c r="H7">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="I7">
-        <v>10.2</v>
+        <v>15.4</v>
       </c>
       <c r="J7">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>82.2</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0.6</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="D8">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="E8">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>20.4</v>
+        <v>15.3</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>17.1</v>
       </c>
       <c r="I8">
-        <v>15.8</v>
+        <v>12.7</v>
       </c>
       <c r="J8">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M8">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="N8">
-        <v>70.40000000000001</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>13.8</v>
       </c>
       <c r="F9">
-        <v>3.4</v>
+        <v>14.7</v>
       </c>
       <c r="G9">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="H9">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="I9">
-        <v>22.1</v>
+        <v>13.3</v>
       </c>
       <c r="J9">
-        <v>22.6</v>
+        <v>12</v>
       </c>
       <c r="K9">
-        <v>15.2</v>
+        <v>7.8</v>
       </c>
       <c r="L9">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="N9">
-        <v>29.7</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="G10">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="H10">
-        <v>9.5</v>
+        <v>12.1</v>
       </c>
       <c r="I10">
-        <v>17.5</v>
+        <v>16.2</v>
       </c>
       <c r="J10">
-        <v>23.8</v>
+        <v>21.5</v>
       </c>
       <c r="K10">
-        <v>18.4</v>
+        <v>19.3</v>
       </c>
       <c r="L10">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="N10">
-        <v>20.3</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E11">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="F11">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="G11">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11">
-        <v>15.4</v>
+        <v>12.2</v>
       </c>
       <c r="J11">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="K11">
-        <v>24.5</v>
+        <v>29</v>
       </c>
       <c r="L11">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="M11">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="N11">
-        <v>8.5</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0.2</v>
+      </c>
+      <c r="G12">
         <v>0.1</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>0.5</v>
       </c>
-      <c r="G12">
-        <v>0.5</v>
-      </c>
-      <c r="H12">
-        <v>2.8</v>
-      </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J12">
-        <v>11.2</v>
+        <v>2.7</v>
       </c>
       <c r="K12">
-        <v>21.6</v>
+        <v>11.1</v>
       </c>
       <c r="L12">
-        <v>31.4</v>
+        <v>37.4</v>
       </c>
       <c r="M12">
-        <v>25.3</v>
+        <v>46.9</v>
       </c>
       <c r="N12">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2396,28 +2477,28 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H13">
         <v>0.5</v>
       </c>
       <c r="I13">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="K13">
-        <v>13.2</v>
+        <v>8.5</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>40.6</v>
       </c>
       <c r="M13">
-        <v>55.1</v>
+        <v>46.7</v>
       </c>
       <c r="N13">
         <v>0.7</v>
@@ -2430,58 +2511,67 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="C2">
+        <v>99.3</v>
+      </c>
+      <c r="D2">
+        <v>99.7</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>99.2</v>
-      </c>
-      <c r="C2">
+      <c r="B3">
+        <v>99</v>
+      </c>
+      <c r="C3">
         <v>100</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E2">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="C3">
+      <c r="E3">
         <v>99.5</v>
       </c>
-      <c r="D3">
-        <v>99.3</v>
-      </c>
-      <c r="E3">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -2492,163 +2582,193 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>96.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E4">
-        <v>96.39999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>89.2</v>
+      </c>
+      <c r="F4">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>96</v>
+        <v>17.2</v>
       </c>
       <c r="C5">
-        <v>62.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D5">
-        <v>91.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E5">
-        <v>93.60000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>84.3</v>
+      </c>
+      <c r="F5">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="C6">
-        <v>90.2</v>
+        <v>89.7</v>
       </c>
       <c r="D6">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="E6">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F6">
+        <v>70.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>96.5</v>
+      </c>
+      <c r="C7">
+        <v>66.60000000000001</v>
+      </c>
+      <c r="D7">
+        <v>91.3</v>
+      </c>
+      <c r="E7">
+        <v>63.8</v>
+      </c>
+      <c r="F7">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>96.8</v>
+      </c>
+      <c r="C8">
+        <v>93.8</v>
+      </c>
+      <c r="D8">
+        <v>34.4</v>
+      </c>
+      <c r="E8">
+        <v>62.8</v>
+      </c>
+      <c r="F8">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>39.6</v>
+      </c>
+      <c r="D9">
+        <v>21.2</v>
+      </c>
+      <c r="E9">
+        <v>64.7</v>
+      </c>
+      <c r="F9">
+        <v>65.10000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>3.8</v>
+      </c>
+      <c r="C10">
+        <v>0.2</v>
+      </c>
+      <c r="D10">
+        <v>3.1</v>
+      </c>
+      <c r="E10">
+        <v>31.5</v>
+      </c>
+      <c r="F10">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
         <v>95.59999999999999</v>
       </c>
-      <c r="E6">
-        <v>92.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>15.9</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>78.10000000000001</v>
-      </c>
-      <c r="E7">
-        <v>83.89999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>94.69999999999999</v>
-      </c>
-      <c r="C8">
-        <v>32.8</v>
-      </c>
-      <c r="D8">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="E8">
-        <v>68.10000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>97.89999999999999</v>
-      </c>
-      <c r="C9">
-        <v>94.69999999999999</v>
-      </c>
-      <c r="D9">
-        <v>33.90000000000001</v>
-      </c>
-      <c r="E9">
-        <v>29.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>0.1</v>
-      </c>
-      <c r="C10">
-        <v>38.2</v>
-      </c>
-      <c r="D10">
-        <v>23.2</v>
-      </c>
-      <c r="E10">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
+      <c r="C11">
+        <v>29.4</v>
+      </c>
+      <c r="D11">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="E11">
+        <v>26.7</v>
+      </c>
+      <c r="F11">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>36.5</v>
-      </c>
-      <c r="C11">
-        <v>58.7</v>
-      </c>
-      <c r="D11">
-        <v>7.9</v>
-      </c>
-      <c r="E11">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B12">
-        <v>3.8</v>
+        <v>38.3</v>
       </c>
       <c r="C12">
-        <v>0.3</v>
+        <v>60.6</v>
       </c>
       <c r="D12">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="E12">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>0.4</v>
+      </c>
+      <c r="F12">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>45</v>
+        <v>43.4</v>
       </c>
       <c r="C13">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="D13">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E13">
-        <v>0.8999999999999999</v>
+        <v>0.2</v>
+      </c>
+      <c r="F13">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2663,28 +2783,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2692,28 +2812,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <v>135.32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>119</v>
+      </c>
+      <c r="G2">
+        <v>0.475</v>
+      </c>
+      <c r="H2">
+        <v>1.4</v>
+      </c>
+      <c r="I2">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2">
-        <v>92.05</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>119.6</v>
-      </c>
-      <c r="G2">
-        <v>0.515</v>
-      </c>
-      <c r="H2">
-        <v>1.7</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2721,28 +2841,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>102.4</v>
+        <v>94.41</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>118.66</v>
+        <v>119</v>
       </c>
       <c r="G3">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2750,28 +2870,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>105.9</v>
+        <v>121.54</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>118.34</v>
+        <v>118.48</v>
       </c>
       <c r="G4">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2779,28 +2899,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>104.15</v>
+        <v>113.39</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>118.5</v>
+        <v>118.48</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.475</v>
       </c>
       <c r="H5">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2808,28 +2928,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>110.47</v>
+        <v>113.47</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>117.93</v>
+        <v>119.16</v>
       </c>
       <c r="G6">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2837,28 +2957,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>123.61</v>
+        <v>114.73</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>116.73</v>
+        <v>119.16</v>
       </c>
       <c r="G7">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2866,28 +2986,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>127.8</v>
+        <v>101.46</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>116.35</v>
+        <v>119.47</v>
       </c>
       <c r="G8">
-        <v>0.455</v>
+        <v>0.525</v>
       </c>
       <c r="H8">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2895,28 +3015,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>124.55</v>
+        <v>123.59</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
       </c>
       <c r="F9">
-        <v>116.65</v>
+        <v>119.47</v>
       </c>
       <c r="G9">
-        <v>0.485</v>
+        <v>0.525</v>
       </c>
       <c r="H9">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2924,28 +3044,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>125.67</v>
+        <v>119.03</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>116.55</v>
+        <v>116.47</v>
       </c>
       <c r="G10">
-        <v>0.515</v>
+        <v>0.475</v>
       </c>
       <c r="H10">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2956,25 +3076,25 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>141.93</v>
+        <v>136.05</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11">
-        <v>115.07</v>
+        <v>116.47</v>
       </c>
       <c r="G11">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H11">
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2982,28 +3102,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12">
-        <v>128.72</v>
+        <v>116.3</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>116.27</v>
+        <v>117.3</v>
       </c>
       <c r="G12">
-        <v>0.485</v>
+        <v>0.55</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3011,28 +3131,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>120.43</v>
+        <v>130.47</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>117.02</v>
+        <v>117.3</v>
       </c>
       <c r="G13">
-        <v>0.515</v>
+        <v>0.55</v>
       </c>
       <c r="H13">
-        <v>-1.3</v>
+        <v>-2</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3047,89 +3167,89 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>141.9266666666666</v>
+        <v>135.32</v>
       </c>
       <c r="E2">
-        <v>425.78</v>
+        <v>541.28</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>127.8</v>
+        <v>136.05</v>
       </c>
       <c r="E3">
-        <v>383.4</v>
+        <v>544.1999999999999</v>
       </c>
       <c r="F3">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3137,57 +3257,57 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>128.72</v>
+        <v>123.585</v>
       </c>
       <c r="E4">
-        <v>386.16</v>
+        <v>494.34</v>
       </c>
       <c r="F4">
-        <v>96.89999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D5">
-        <v>124.5466666666667</v>
+        <v>130.475</v>
       </c>
       <c r="E5">
-        <v>373.64</v>
+        <v>521.9</v>
       </c>
       <c r="F5">
-        <v>94.8</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3195,112 +3315,112 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>123.6133333333333</v>
+        <v>121.54</v>
       </c>
       <c r="E6">
-        <v>370.84</v>
+        <v>486.16</v>
       </c>
       <c r="F6">
-        <v>93.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D7">
-        <v>125.6666666666667</v>
+        <v>113.385</v>
       </c>
       <c r="E7">
-        <v>377</v>
+        <v>453.5400000000001</v>
       </c>
       <c r="F7">
-        <v>82.19999999999999</v>
+        <v>66.10000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D8">
-        <v>120.4266666666667</v>
+        <v>113.465</v>
       </c>
       <c r="E8">
-        <v>361.28</v>
+        <v>453.86</v>
       </c>
       <c r="F8">
-        <v>70.39999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G8">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>105.9</v>
+        <v>119.03</v>
       </c>
       <c r="E9">
-        <v>317.7</v>
+        <v>476.12</v>
       </c>
       <c r="F9">
-        <v>29.7</v>
+        <v>65.3</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
         <v>87</v>
@@ -3308,118 +3428,118 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>102.4</v>
+        <v>116.305</v>
       </c>
       <c r="E10">
-        <v>307.2</v>
+        <v>465.2199999999999</v>
       </c>
       <c r="F10">
-        <v>20.3</v>
+        <v>34.7</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>110.4733333333333</v>
+        <v>114.735</v>
       </c>
       <c r="E11">
-        <v>331.42</v>
+        <v>458.9399999999999</v>
       </c>
       <c r="F11">
-        <v>8.5</v>
+        <v>23.9</v>
       </c>
       <c r="G11">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D12">
-        <v>104.1466666666666</v>
+        <v>94.41</v>
       </c>
       <c r="E12">
-        <v>312.4399999999999</v>
+        <v>377.64</v>
       </c>
       <c r="F12">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>25.3</v>
+        <v>46.9</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C13">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>92.04666666666667</v>
+        <v>101.46</v>
       </c>
       <c r="E13">
-        <v>276.14</v>
+        <v>405.84</v>
       </c>
       <c r="F13">
         <v>0.7000000000000001</v>
       </c>
       <c r="G13">
-        <v>55.1</v>
+        <v>46.7</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3434,19 +3554,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3454,19 +3574,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3474,19 +3594,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3497,16 +3617,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3514,19 +3634,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3534,19 +3654,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3557,16 +3677,16 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3574,19 +3694,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3594,7 +3714,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
@@ -3603,10 +3723,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3614,19 +3734,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3637,16 +3757,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3657,7 +3777,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>-17</v>
@@ -3666,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3677,13 +3797,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D13">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>105</v>
@@ -3696,10 +3816,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
         <v>106</v>
       </c>
@@ -3710,44 +3830,53 @@
         <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>109</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>-2</v>
+      </c>
+      <c r="C2">
+        <v>-4</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>9</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>9</v>
       </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
       <c r="D3">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3760,13 +3889,16 @@
       <c r="D4">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <v>-2</v>
@@ -3775,30 +3907,36 @@
         <v>-4</v>
       </c>
       <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="E5">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -3811,62 +3949,74 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>-1</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>-2</v>
-      </c>
-      <c r="C10">
-        <v>-4</v>
-      </c>
       <c r="D10">
-        <v>-1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>-8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3879,11 +4029,14 @@
       <c r="D11">
         <v>-10</v>
       </c>
-      <c r="E11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11">
+        <v>-8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -3896,11 +4049,14 @@
       <c r="D12">
         <v>-17</v>
       </c>
-      <c r="E12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12">
+        <v>-17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3913,7 +4069,10 @@
       <c r="D13">
         <v>-19</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13">
+        <v>-18</v>
+      </c>
+      <c r="F13" t="s">
         <v>105</v>
       </c>
     </row>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="117">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,19 +61,22 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -172,13 +178,16 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Michael  Celoni</t>
+  </si>
+  <si>
+    <t>Joseph Wood</t>
+  </si>
+  <si>
     <t>Chris Holloway</t>
   </si>
   <si>
-    <t>Michael  Celoni</t>
-  </si>
-  <si>
-    <t>Joseph Wood</t>
+    <t>Robbie Wilston</t>
   </si>
   <si>
     <t>Chris Carbone</t>
@@ -187,21 +196,18 @@
     <t>Colman Closser</t>
   </si>
   <si>
+    <t>Shane Leiphart</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
     <t>Tomas Angel</t>
   </si>
   <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Shane Leiphart</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
     <t>Eli Brinker</t>
   </si>
   <si>
@@ -229,55 +235,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>10.9-3.0-0.1</t>
-  </si>
-  <si>
-    <t>10.3-3.6-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>11.1-2.8-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
   </si>
   <si>
     <t>8.3-5.6-0.1</t>
   </si>
   <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.6-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>3.2-10.8-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.3-7.6-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>3.2-10.7-0.1</t>
+  </si>
+  <si>
+    <t>3.3-10.6-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -313,36 +313,33 @@
     <t>↑6</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↓2</t>
   </si>
   <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>↓8</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -353,6 +350,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -789,7 +789,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -827,22 +827,22 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -851,7 +851,7 @@
         <v>14</v>
       </c>
       <c r="M3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -862,7 +862,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -871,28 +871,28 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -903,34 +903,34 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="L5" t="s">
         <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -956,13 +956,13 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -982,13 +982,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -997,25 +997,25 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" t="s">
-        <v>14</v>
-      </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1032,31 +1032,31 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
         <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1067,37 +1067,37 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
         <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1111,7 +1111,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -1120,25 +1120,25 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
         <v>16</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
-      </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1164,10 +1164,10 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
         <v>14</v>
@@ -1196,16 +1196,16 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -1220,7 +1220,7 @@
         <v>12</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1237,31 +1237,31 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L13" t="s">
         <v>14</v>
       </c>
       <c r="M13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1328,25 +1328,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1354,25 +1354,25 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
       <c r="E4">
-        <v>11</v>
+        <v>-16</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,25 +1380,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
       <c r="E5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1406,25 +1406,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1435,22 +1435,22 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1458,25 +1458,25 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>-10</v>
       </c>
       <c r="F8">
+        <v>-17</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="H8" t="s">
         <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1484,24 +1484,102 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>-10</v>
+      </c>
+      <c r="F9">
+        <v>-4</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E9">
+      <c r="E12">
         <v>11</v>
       </c>
-      <c r="F9">
+      <c r="F12">
         <v>7</v>
       </c>
-      <c r="G9">
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1517,13 +1595,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1531,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1545,13 +1623,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1562,7 +1640,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1573,13 +1651,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1.833333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1587,13 +1665,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1601,13 +1679,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1615,13 +1693,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.083333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1629,13 +1707,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>2.083333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1646,7 +1724,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>2.416666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -1660,10 +1738,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>2.583333333333333</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1674,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>2.583333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1688,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>3.416666666666667</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1706,16 +1784,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1726,7 +1804,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="D2">
         <v>0.25</v>
@@ -1740,16 +1818,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>2.916666666666667</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D3">
-        <v>-1.083333333333333</v>
+        <v>-0.9166666666666665</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1757,16 +1835,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1774,13 +1852,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>2.25</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D5">
-        <v>-0.75</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1791,16 +1869,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2.083333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D6">
-        <v>0.08333333333333348</v>
+        <v>-1.25</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1808,16 +1886,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1828,10 +1906,10 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -1842,16 +1920,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>1.916666666666667</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D9">
-        <v>-1.083333333333333</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1859,16 +1937,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.75</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D10">
-        <v>0.75</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1876,16 +1954,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1.583333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="D11">
-        <v>0.5833333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1893,16 +1971,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D12">
-        <v>1.333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1913,10 +1991,10 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>0.5833333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D13">
-        <v>-0.4166666666666666</v>
+        <v>-0.08333333333333337</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -1934,81 +2012,81 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>54.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C2">
-        <v>30.5</v>
+        <v>12.6</v>
       </c>
       <c r="D2">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
       <c r="E2">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2017,42 +2095,42 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>37.1</v>
+        <v>8.5</v>
       </c>
       <c r="C3">
-        <v>39.3</v>
+        <v>33.2</v>
       </c>
       <c r="D3">
-        <v>13.2</v>
+        <v>19.1</v>
       </c>
       <c r="E3">
-        <v>6.4</v>
+        <v>15.1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>8.6</v>
       </c>
       <c r="G3">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2061,139 +2139,139 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4">
+        <v>2.4</v>
+      </c>
+      <c r="C4">
+        <v>15.8</v>
+      </c>
+      <c r="D4">
+        <v>22.5</v>
+      </c>
+      <c r="E4">
+        <v>16.6</v>
+      </c>
+      <c r="F4">
+        <v>12.7</v>
+      </c>
+      <c r="G4">
+        <v>10.4</v>
+      </c>
+      <c r="H4">
+        <v>9.5</v>
+      </c>
+      <c r="I4">
+        <v>5.9</v>
+      </c>
+      <c r="J4">
         <v>3.6</v>
       </c>
-      <c r="C4">
-        <v>11.1</v>
-      </c>
-      <c r="D4">
-        <v>24.9</v>
-      </c>
-      <c r="E4">
-        <v>16.2</v>
-      </c>
-      <c r="F4">
-        <v>12.5</v>
-      </c>
-      <c r="G4">
-        <v>11.9</v>
-      </c>
-      <c r="H4">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I4">
-        <v>6.8</v>
-      </c>
-      <c r="J4">
-        <v>3.3</v>
-      </c>
       <c r="K4">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="L4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>88.5</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="D5">
-        <v>16.3</v>
+        <v>19.2</v>
       </c>
       <c r="E5">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="F5">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>10.8</v>
       </c>
       <c r="H5">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="L5">
         <v>0.3</v>
       </c>
       <c r="M5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>81.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>13.4</v>
+      </c>
+      <c r="D6">
+        <v>15.7</v>
+      </c>
+      <c r="E6">
+        <v>17.4</v>
+      </c>
+      <c r="F6">
+        <v>16.4</v>
+      </c>
+      <c r="G6">
+        <v>13.1</v>
+      </c>
+      <c r="H6">
+        <v>8.5</v>
+      </c>
+      <c r="I6">
+        <v>7.4</v>
+      </c>
+      <c r="J6">
+        <v>3.3</v>
+      </c>
+      <c r="K6">
         <v>1.5</v>
       </c>
-      <c r="C6">
-        <v>2.6</v>
-      </c>
-      <c r="D6">
-        <v>9.6</v>
-      </c>
-      <c r="E6">
-        <v>15.5</v>
-      </c>
-      <c r="F6">
-        <v>16.2</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>13.7</v>
-      </c>
-      <c r="I6">
-        <v>12.6</v>
-      </c>
-      <c r="J6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K6">
-        <v>5.5</v>
-      </c>
       <c r="L6">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>73.09999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2201,224 +2279,224 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C7">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="E7">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="F7">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="G7">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="H7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>15.4</v>
+        <v>16.1</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="K7">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N7">
-        <v>66.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G8">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="H8">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="I8">
-        <v>12.7</v>
+        <v>17.4</v>
       </c>
       <c r="J8">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="K8">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="M8">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N8">
-        <v>65.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>0.2</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D9">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>13.8</v>
+        <v>7.3</v>
       </c>
       <c r="F9">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="G9">
-        <v>13.4</v>
+        <v>14.5</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="I9">
-        <v>13.3</v>
+        <v>16.3</v>
       </c>
       <c r="J9">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="K9">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="M9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N9">
-        <v>65.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D10">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="F10">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="H10">
-        <v>12.1</v>
+        <v>15.4</v>
       </c>
       <c r="I10">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="J10">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="K10">
-        <v>19.3</v>
+        <v>13.1</v>
       </c>
       <c r="L10">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="M10">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>34.7</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0.6</v>
       </c>
-      <c r="D11">
-        <v>1.2</v>
-      </c>
-      <c r="E11">
-        <v>3.1</v>
-      </c>
       <c r="F11">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H11">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>20.2</v>
+        <v>17.8</v>
       </c>
       <c r="K11">
-        <v>29</v>
+        <v>36.7</v>
       </c>
       <c r="L11">
-        <v>11.8</v>
+        <v>19.2</v>
       </c>
       <c r="M11">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="N11">
-        <v>23.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2436,33 +2514,33 @@
         <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I12">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J12">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="K12">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="L12">
-        <v>37.4</v>
+        <v>37.8</v>
       </c>
       <c r="M12">
-        <v>46.9</v>
+        <v>39.1</v>
       </c>
       <c r="N12">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2480,25 +2558,25 @@
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I13">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>8.5</v>
+        <v>13.1</v>
       </c>
       <c r="L13">
-        <v>40.6</v>
+        <v>31.1</v>
       </c>
       <c r="M13">
-        <v>46.7</v>
+        <v>50.1</v>
       </c>
       <c r="N13">
         <v>0.7</v>
@@ -2511,264 +2589,303 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>87.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C2">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="E2">
+        <v>99.8</v>
+      </c>
+      <c r="F2">
         <v>100</v>
       </c>
-      <c r="F2">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>95.89999999999999</v>
       </c>
       <c r="E3">
-        <v>99.5</v>
+        <v>90.8</v>
       </c>
       <c r="F3">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>97.5</v>
+      </c>
+      <c r="G3">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="D4">
-        <v>95.5</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="E4">
+        <v>64.2</v>
+      </c>
+      <c r="F4">
+        <v>90.3</v>
+      </c>
+      <c r="G4">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="C5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D5">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F5">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="G5">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>39.1</v>
+      </c>
+      <c r="D6">
+        <v>20.9</v>
+      </c>
+      <c r="E6">
+        <v>63.5</v>
+      </c>
+      <c r="F6">
+        <v>86.8</v>
+      </c>
+      <c r="G6">
         <v>89.2</v>
       </c>
-      <c r="F4">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>97.3</v>
+      </c>
+      <c r="C7">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="D7">
+        <v>32.1</v>
+      </c>
+      <c r="E7">
+        <v>61.2</v>
+      </c>
+      <c r="F7">
+        <v>65.2</v>
+      </c>
+      <c r="G7">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>20.9</v>
+      </c>
+      <c r="C8">
         <v>89.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="D8">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E8">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="F8">
+        <v>58.8</v>
+      </c>
+      <c r="G8">
+        <v>57.49999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>17.2</v>
-      </c>
-      <c r="C5">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D5">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E5">
-        <v>84.3</v>
-      </c>
-      <c r="F5">
-        <v>83.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>22.3</v>
-      </c>
-      <c r="C6">
-        <v>89.7</v>
-      </c>
-      <c r="D6">
-        <v>94.19999999999999</v>
-      </c>
-      <c r="E6">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="F6">
-        <v>70.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>96.5</v>
-      </c>
-      <c r="C7">
-        <v>66.60000000000001</v>
-      </c>
-      <c r="D7">
-        <v>91.3</v>
-      </c>
-      <c r="E7">
-        <v>63.8</v>
-      </c>
-      <c r="F7">
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>96.8</v>
-      </c>
-      <c r="C8">
-        <v>93.8</v>
-      </c>
-      <c r="D8">
-        <v>34.4</v>
-      </c>
-      <c r="E8">
-        <v>62.8</v>
-      </c>
-      <c r="F8">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B9">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="C9">
-        <v>39.6</v>
+        <v>9.1</v>
       </c>
       <c r="D9">
-        <v>21.2</v>
+        <v>79.2</v>
       </c>
       <c r="E9">
-        <v>64.7</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>65.10000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>61.3</v>
+      </c>
+      <c r="G9">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B10">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="C10">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>72.3</v>
+      </c>
+      <c r="E10">
+        <v>27.6</v>
+      </c>
+      <c r="F10">
+        <v>38.7</v>
+      </c>
+      <c r="G10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>4.9</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
         <v>3.8</v>
       </c>
-      <c r="C10">
-        <v>0.2</v>
-      </c>
-      <c r="D10">
-        <v>3.1</v>
-      </c>
-      <c r="E10">
-        <v>31.5</v>
-      </c>
-      <c r="F10">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="C11">
-        <v>29.4</v>
-      </c>
-      <c r="D11">
-        <v>71.59999999999999</v>
-      </c>
       <c r="E11">
-        <v>26.7</v>
+        <v>33.7</v>
       </c>
       <c r="F11">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G11">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B12">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="C12">
-        <v>60.6</v>
+        <v>61.5</v>
       </c>
       <c r="D12">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="E12">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.5</v>
+      </c>
+      <c r="G12">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>43.4</v>
+        <v>42.8</v>
       </c>
       <c r="C13">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E13">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="G13">
+        <v>0.8999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2783,28 +2900,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2815,25 +2932,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>135.32</v>
+        <v>122.8</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>119</v>
+        <v>122.27</v>
       </c>
       <c r="G2">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2841,28 +2958,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>94.41</v>
+        <v>121.69</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>119</v>
+        <v>120.3</v>
       </c>
       <c r="G3">
-        <v>0.475</v>
+        <v>0.444</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2870,28 +2987,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>121.54</v>
+        <v>110.88</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>118.48</v>
+        <v>119.81</v>
       </c>
       <c r="G4">
-        <v>0.475</v>
+        <v>0.444</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2899,28 +3016,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>113.39</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>118.48</v>
+        <v>120.35</v>
       </c>
       <c r="G5">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2928,28 +3045,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>113.47</v>
+        <v>128.1</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6">
-        <v>119.16</v>
+        <v>122.26</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2957,28 +3074,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>114.73</v>
+        <v>118.4</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>119.16</v>
+        <v>119.66</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2986,28 +3103,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>101.46</v>
+        <v>116.65</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>119.47</v>
+        <v>118.92</v>
       </c>
       <c r="G8">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3015,28 +3132,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>123.59</v>
+        <v>145.5</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
       </c>
       <c r="F9">
-        <v>119.47</v>
+        <v>117.51</v>
       </c>
       <c r="G9">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3044,28 +3161,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>119.03</v>
+        <v>111.15</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>116.47</v>
+        <v>118.81</v>
       </c>
       <c r="G10">
-        <v>0.475</v>
+        <v>0.556</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3073,28 +3190,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>136.05</v>
+        <v>105.62</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>116.47</v>
+        <v>117.16</v>
       </c>
       <c r="G11">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>-2.2</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3102,28 +3219,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>116.3</v>
+        <v>124.97</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>117.3</v>
+        <v>116.9</v>
       </c>
       <c r="G12">
-        <v>0.55</v>
+        <v>0.489</v>
       </c>
       <c r="H12">
-        <v>-2</v>
+        <v>-2.6</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3134,25 +3251,25 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>130.47</v>
+        <v>128.33</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>117.3</v>
+        <v>119.73</v>
       </c>
       <c r="G13">
-        <v>0.55</v>
+        <v>0.578</v>
       </c>
       <c r="H13">
-        <v>-2</v>
+        <v>-3.2</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3167,57 +3284,57 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>135.32</v>
+        <v>145.5</v>
       </c>
       <c r="E2">
-        <v>541.28</v>
+        <v>727.5</v>
       </c>
       <c r="F2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
         <v>85</v>
@@ -3225,86 +3342,86 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>136.05</v>
+        <v>128.104</v>
       </c>
       <c r="E3">
-        <v>544.1999999999999</v>
+        <v>640.52</v>
       </c>
       <c r="F3">
-        <v>99.7</v>
+        <v>95.3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>123.585</v>
+        <v>124.968</v>
       </c>
       <c r="E4">
-        <v>494.34</v>
+        <v>624.84</v>
       </c>
       <c r="F4">
-        <v>88.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="D5">
-        <v>130.475</v>
+        <v>122.8</v>
       </c>
       <c r="E5">
-        <v>521.9</v>
+        <v>614</v>
       </c>
       <c r="F5">
-        <v>81.89999999999999</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="G5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
         <v>87</v>
@@ -3312,28 +3429,28 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D6">
-        <v>121.54</v>
+        <v>118.404</v>
       </c>
       <c r="E6">
-        <v>486.16</v>
+        <v>592.02</v>
       </c>
       <c r="F6">
-        <v>73.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
         <v>87</v>
@@ -3344,54 +3461,54 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>113.385</v>
+        <v>110.876</v>
       </c>
       <c r="E7">
-        <v>453.5400000000001</v>
+        <v>554.3800000000001</v>
       </c>
       <c r="F7">
-        <v>66.10000000000001</v>
+        <v>68.89999999999999</v>
       </c>
       <c r="G7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>113.465</v>
+        <v>121.692</v>
       </c>
       <c r="E8">
-        <v>453.86</v>
+        <v>608.4599999999999</v>
       </c>
       <c r="F8">
-        <v>65.5</v>
+        <v>58.3</v>
       </c>
       <c r="G8">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
         <v>88</v>
@@ -3399,54 +3516,54 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>119.03</v>
+        <v>128.328</v>
       </c>
       <c r="E9">
-        <v>476.12</v>
+        <v>641.64</v>
       </c>
       <c r="F9">
-        <v>65.3</v>
+        <v>56.2</v>
       </c>
       <c r="G9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>116.305</v>
+        <v>116.648</v>
       </c>
       <c r="E10">
-        <v>465.2199999999999</v>
+        <v>583.2399999999999</v>
       </c>
       <c r="F10">
-        <v>34.7</v>
+        <v>42.7</v>
       </c>
       <c r="G10">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="s">
         <v>81</v>
@@ -3457,25 +3574,25 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>114.735</v>
+        <v>111.148</v>
       </c>
       <c r="E11">
-        <v>458.9399999999999</v>
+        <v>555.7399999999999</v>
       </c>
       <c r="F11">
-        <v>23.9</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="G11">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="H11" t="s">
         <v>82</v>
@@ -3486,25 +3603,25 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>94.41</v>
+        <v>105.62</v>
       </c>
       <c r="E12">
-        <v>377.64</v>
+        <v>528.1</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
-        <v>46.9</v>
+        <v>39.1</v>
       </c>
       <c r="H12" t="s">
         <v>83</v>
@@ -3515,25 +3632,25 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>101.46</v>
+        <v>99.604</v>
       </c>
       <c r="E13">
-        <v>405.84</v>
+        <v>498.02</v>
       </c>
       <c r="F13">
         <v>0.7000000000000001</v>
       </c>
       <c r="G13">
-        <v>46.7</v>
+        <v>50.1</v>
       </c>
       <c r="H13" t="s">
         <v>84</v>
@@ -3554,7 +3671,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>92</v>
@@ -3563,7 +3680,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>94</v>
@@ -3574,16 +3691,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>95</v>
@@ -3597,13 +3714,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
         <v>96</v>
@@ -3614,16 +3731,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>97</v>
@@ -3634,16 +3751,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>98</v>
@@ -3654,16 +3771,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>99</v>
@@ -3674,16 +3791,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>100</v>
@@ -3697,13 +3814,13 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
         <v>101</v>
@@ -3714,16 +3831,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
         <v>102</v>
@@ -3734,16 +3851,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>103</v>
@@ -3754,19 +3871,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3774,19 +3891,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
         <v>52</v>
       </c>
       <c r="D12">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3797,16 +3914,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3816,47 +3933,53 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3872,91 +3995,106 @@
       <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>-2</v>
+      </c>
+      <c r="C4">
+        <v>-4</v>
+      </c>
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>-2</v>
+      </c>
+      <c r="C6">
+        <v>-4</v>
+      </c>
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>-2</v>
-      </c>
-      <c r="C5">
-        <v>-4</v>
-      </c>
-      <c r="D5">
+      <c r="B7">
         <v>-1</v>
       </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
       <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -3972,91 +4110,106 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>-8</v>
+      </c>
+      <c r="F9">
+        <v>-4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="B9">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>-6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>-10</v>
+      </c>
+      <c r="C11">
+        <v>-10</v>
+      </c>
+      <c r="D11">
+        <v>-17</v>
+      </c>
+      <c r="E11">
+        <v>-17</v>
+      </c>
+      <c r="F11">
+        <v>-13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
         <v>-1</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="D12">
+        <v>-10</v>
+      </c>
+      <c r="E12">
         <v>-8</v>
       </c>
-      <c r="F10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>-1</v>
-      </c>
-      <c r="D11">
-        <v>-10</v>
-      </c>
-      <c r="E11">
-        <v>-8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F12">
+        <v>-16</v>
+      </c>
+      <c r="G12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>-10</v>
-      </c>
-      <c r="C12">
-        <v>-10</v>
-      </c>
-      <c r="D12">
-        <v>-17</v>
-      </c>
-      <c r="E12">
-        <v>-17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -4072,8 +4225,11 @@
       <c r="E13">
         <v>-18</v>
       </c>
-      <c r="F13" t="s">
-        <v>105</v>
+      <c r="F13">
+        <v>-17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="124">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,22 +61,25 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -154,6 +157,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -178,39 +184,39 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Shane Leiphart</t>
+  </si>
+  <si>
     <t>Michael  Celoni</t>
   </si>
   <si>
+    <t>Chris Holloway</t>
+  </si>
+  <si>
     <t>Joseph Wood</t>
   </si>
   <si>
-    <t>Chris Holloway</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
+    <t>Prahlad Singh</t>
   </si>
   <si>
     <t>Chris Carbone</t>
   </si>
   <si>
+    <t>Eli Brinker</t>
+  </si>
+  <si>
+    <t>Tomas Angel</t>
+  </si>
+  <si>
     <t>Colman Closser</t>
   </si>
   <si>
-    <t>Shane Leiphart</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Tomas Angel</t>
-  </si>
-  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Eli Brinker</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -235,49 +241,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>10.5-3.5-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
   </si>
   <si>
     <t>9.1-4.8-0.1</t>
   </si>
   <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>7.6-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
   </si>
   <si>
     <t>6.3-7.6-0.1</t>
   </si>
   <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>3.2-10.7-0.1</t>
-  </si>
-  <si>
-    <t>3.3-10.6-0.1</t>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.7-0.1</t>
+  </si>
+  <si>
+    <t>2.9-11.0-0.1</t>
+  </si>
+  <si>
+    <t>2.6-11.3-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -301,6 +313,9 @@
     <t>3-11</t>
   </si>
   <si>
+    <t>2-12</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -310,34 +325,37 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑6</t>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑3</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓10</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>↓11</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -353,6 +371,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -780,37 +801,37 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -824,34 +845,34 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
         <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -859,40 +880,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -909,31 +930,31 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
       </c>
       <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
         <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -941,40 +962,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
         <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -982,40 +1003,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="K7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>14</v>
-      </c>
       <c r="L7" t="s">
         <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1023,40 +1044,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
       <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
       <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L8" t="s">
         <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1064,13 +1085,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -1085,19 +1106,19 @@
         <v>17</v>
       </c>
       <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
         <v>15</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
         <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1108,28 +1129,28 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
       <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>17</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
         <v>16</v>
@@ -1138,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1149,37 +1170,37 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s">
         <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1196,31 +1217,31 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" t="s">
         <v>14</v>
-      </c>
-      <c r="J12" t="s">
-        <v>12</v>
       </c>
       <c r="K12" t="s">
         <v>13</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1228,40 +1249,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" t="s">
-        <v>14</v>
-      </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1271,30 +1292,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1328,25 +1349,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1357,22 +1378,22 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>-16</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,22 +1401,22 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="F5">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
         <v>4</v>
@@ -1406,22 +1427,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -1432,25 +1453,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1458,25 +1479,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
       <c r="E8">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1487,22 +1508,22 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1510,25 +1531,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
       <c r="D10" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>-10</v>
       </c>
       <c r="F10">
+        <v>-17</v>
+      </c>
+      <c r="G10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="H10" t="s">
         <v>6</v>
-      </c>
-      <c r="H10" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1536,25 +1557,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11">
+        <v>-10</v>
+      </c>
+      <c r="F11">
+        <v>-4</v>
+      </c>
+      <c r="G11">
         <v>6</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
       <c r="H11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1562,24 +1583,102 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>-3</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>7</v>
+      </c>
+      <c r="G15">
         <v>4</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H15" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1595,13 +1694,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1609,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1.166666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1623,13 +1722,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1.416666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1640,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1.666666666666667</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1651,13 +1750,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2.083333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1665,13 +1764,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2.333333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1679,10 +1778,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2.333333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -1693,13 +1792,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>2.416666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1710,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>2.916666666666667</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -1721,13 +1820,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>2.916666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1738,10 +1837,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>3.416666666666667</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1749,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>3.5</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1766,10 +1865,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>3.833333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1784,16 +1883,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1804,13 +1903,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.25</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>-0.583333333333333</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1818,16 +1917,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>3.083333333333333</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.9166666666666665</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1835,13 +1934,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1855,13 +1954,13 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>2.916666666666667</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D5">
-        <v>-1.083333333333333</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1869,16 +1968,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2.75</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D6">
-        <v>-1.25</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1886,16 +1985,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2.583333333333333</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D7">
-        <v>1.583333333333333</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1906,13 +2005,13 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1920,16 +2019,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.416666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D9">
-        <v>0.4166666666666665</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1937,16 +2036,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>2.166666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D10">
-        <v>-1.833333333333333</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1954,16 +2053,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1.75</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D11">
-        <v>1.75</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1971,16 +2070,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1997,7 +2096,7 @@
         <v>-0.08333333333333337</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2012,46 +2111,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2059,29 +2158,29 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>80.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="C2">
-        <v>12.6</v>
+        <v>19.5</v>
       </c>
       <c r="D2">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="F2">
+        <v>2.9</v>
+      </c>
+      <c r="G2">
+        <v>1.6</v>
+      </c>
+      <c r="H2">
         <v>0.7</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>0.1</v>
       </c>
-      <c r="H2">
-        <v>0.1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
       <c r="J2">
         <v>0</v>
       </c>
@@ -2095,39 +2194,39 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C3">
-        <v>33.2</v>
+        <v>21.7</v>
       </c>
       <c r="D3">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3">
-        <v>15.1</v>
+        <v>17.4</v>
       </c>
       <c r="F3">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="G3">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J3">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K3">
         <v>0.1</v>
@@ -2139,271 +2238,271 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>95.3</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2.4</v>
+        <v>13.2</v>
       </c>
       <c r="C4">
-        <v>15.8</v>
+        <v>19.6</v>
       </c>
       <c r="D4">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="F4">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="G4">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>89.90000000000001</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>4.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C5">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="D5">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="E5">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="F5">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="G5">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>89.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="C6">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="D6">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
       <c r="E6">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="F6">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="G6">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>10.3</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="K6">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="L6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="C7">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="D7">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="E7">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="F7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>17.8</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="I7">
-        <v>16.1</v>
+        <v>13.2</v>
       </c>
       <c r="J7">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="L7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>68.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="E8">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F8">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="G8">
         <v>15.9</v>
       </c>
       <c r="H8">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="I8">
-        <v>17.4</v>
+        <v>15.6</v>
       </c>
       <c r="J8">
-        <v>15.6</v>
+        <v>12.3</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="M8">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>58.3</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="E9">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="F9">
-        <v>11.3</v>
+        <v>7.6</v>
       </c>
       <c r="G9">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="H9">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="I9">
-        <v>16.3</v>
+        <v>22</v>
       </c>
       <c r="J9">
-        <v>15.5</v>
+        <v>20.5</v>
       </c>
       <c r="K9">
-        <v>8.300000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="L9">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="M9">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N9">
-        <v>56.2</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2411,43 +2510,43 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="E10">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="F10">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="G10">
-        <v>10.4</v>
+        <v>6.9</v>
       </c>
       <c r="H10">
-        <v>15.4</v>
+        <v>12.7</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>19.4</v>
       </c>
       <c r="J10">
-        <v>20.7</v>
+        <v>29.4</v>
       </c>
       <c r="K10">
-        <v>13.1</v>
+        <v>21</v>
       </c>
       <c r="L10">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N10">
-        <v>42.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2458,45 +2557,45 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G11">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="J11">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="K11">
-        <v>36.7</v>
+        <v>44.2</v>
       </c>
       <c r="L11">
-        <v>19.2</v>
+        <v>11</v>
       </c>
       <c r="M11">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="N11">
-        <v>9.699999999999999</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2511,36 +2610,36 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0.2</v>
       </c>
-      <c r="G12">
+      <c r="I12">
+        <v>0.9</v>
+      </c>
+      <c r="J12">
+        <v>2.3</v>
+      </c>
+      <c r="K12">
+        <v>6.8</v>
+      </c>
+      <c r="L12">
+        <v>38.7</v>
+      </c>
+      <c r="M12">
+        <v>51.1</v>
+      </c>
+      <c r="N12">
         <v>0.2</v>
-      </c>
-      <c r="H12">
-        <v>0.8</v>
-      </c>
-      <c r="I12">
-        <v>1.3</v>
-      </c>
-      <c r="J12">
-        <v>5.2</v>
-      </c>
-      <c r="K12">
-        <v>15.4</v>
-      </c>
-      <c r="L12">
-        <v>37.8</v>
-      </c>
-      <c r="M12">
-        <v>39.1</v>
-      </c>
-      <c r="N12">
-        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2555,31 +2654,31 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0.1</v>
       </c>
-      <c r="G13">
-        <v>0.2</v>
-      </c>
-      <c r="H13">
-        <v>0.4</v>
-      </c>
       <c r="I13">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="K13">
-        <v>13.1</v>
+        <v>7.3</v>
       </c>
       <c r="L13">
-        <v>31.1</v>
+        <v>44.2</v>
       </c>
       <c r="M13">
-        <v>50.1</v>
+        <v>45.9</v>
       </c>
       <c r="N13">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2589,35 +2688,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2626,266 +2728,302 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H2">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>90.3</v>
+      </c>
+      <c r="C3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D3">
+        <v>99.8</v>
+      </c>
+      <c r="E3">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3">
-        <v>95.89999999999999</v>
-      </c>
-      <c r="E3">
-        <v>90.8</v>
-      </c>
       <c r="F3">
-        <v>97.5</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="G3">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="H3">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="C4">
+        <v>66.10000000000001</v>
+      </c>
+      <c r="D4">
+        <v>92.5</v>
+      </c>
+      <c r="E4">
+        <v>61.8</v>
+      </c>
+      <c r="F4">
+        <v>90.7</v>
+      </c>
+      <c r="G4">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="H4">
+        <v>94.19999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>97.8</v>
+      </c>
+      <c r="C5">
         <v>94.5</v>
       </c>
-      <c r="C4">
-        <v>63.6</v>
-      </c>
-      <c r="D4">
-        <v>92.60000000000001</v>
-      </c>
-      <c r="E4">
-        <v>64.2</v>
-      </c>
-      <c r="F4">
-        <v>90.3</v>
-      </c>
-      <c r="G4">
-        <v>89.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
+      <c r="D5">
+        <v>34.7</v>
+      </c>
+      <c r="E5">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F5">
+        <v>65.3</v>
+      </c>
+      <c r="G5">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="H5">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>95.7</v>
+      </c>
+      <c r="E6">
         <v>90.60000000000001</v>
       </c>
-      <c r="C5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D5">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="E5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="F5">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="G5">
-        <v>89.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="F6">
+        <v>96.7</v>
+      </c>
+      <c r="G6">
+        <v>93.2</v>
+      </c>
+      <c r="H6">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>39.1</v>
-      </c>
-      <c r="D6">
-        <v>20.9</v>
-      </c>
-      <c r="E6">
-        <v>63.5</v>
-      </c>
-      <c r="F6">
-        <v>86.8</v>
-      </c>
-      <c r="G6">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B7">
-        <v>97.3</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>93.60000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="D7">
-        <v>32.1</v>
+        <v>23.3</v>
       </c>
       <c r="E7">
-        <v>61.2</v>
+        <v>64.5</v>
       </c>
       <c r="F7">
-        <v>65.2</v>
+        <v>85.7</v>
       </c>
       <c r="G7">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="H7">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>16.1</v>
+      </c>
+      <c r="C8">
+        <v>10.8</v>
+      </c>
+      <c r="D8">
+        <v>77.10000000000001</v>
+      </c>
+      <c r="E8">
+        <v>83.89999999999999</v>
+      </c>
+      <c r="F8">
+        <v>62.8</v>
+      </c>
+      <c r="G8">
+        <v>70.19999999999999</v>
+      </c>
+      <c r="H8">
+        <v>67.10000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>20.9</v>
-      </c>
-      <c r="C8">
-        <v>89.3</v>
-      </c>
-      <c r="D8">
+      <c r="B9">
+        <v>22.3</v>
+      </c>
+      <c r="C9">
+        <v>90.10000000000001</v>
+      </c>
+      <c r="D9">
         <v>95.09999999999999</v>
       </c>
-      <c r="E8">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="F8">
-        <v>58.8</v>
-      </c>
-      <c r="G8">
-        <v>57.49999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>16.3</v>
-      </c>
-      <c r="C9">
-        <v>9.1</v>
-      </c>
-      <c r="D9">
-        <v>79.2</v>
-      </c>
       <c r="E9">
-        <v>82</v>
+        <v>76.3</v>
       </c>
       <c r="F9">
-        <v>61.3</v>
+        <v>59.9</v>
       </c>
       <c r="G9">
-        <v>53.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H9">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>95.19999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="C10">
-        <v>31</v>
+        <v>30.2</v>
       </c>
       <c r="D10">
-        <v>72.3</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="E10">
-        <v>27.6</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="G10">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>30.3</v>
+      </c>
+      <c r="H10">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B11">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="C11">
         <v>0.1</v>
       </c>
       <c r="D11">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E11">
-        <v>33.7</v>
+        <v>32.9</v>
       </c>
       <c r="F11">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="G11">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B12">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="C12">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>8.4</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="E12">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>0.3</v>
+      </c>
+      <c r="H12">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>42.8</v>
+        <v>41.3</v>
       </c>
       <c r="C13">
-        <v>12.8</v>
+        <v>10.8</v>
       </c>
       <c r="D13">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E13">
         <v>0.6</v>
       </c>
       <c r="F13">
-        <v>0.7000000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G13">
-        <v>0.8999999999999999</v>
+        <v>0.1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2900,28 +3038,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2932,25 +3070,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>122.8</v>
+        <v>121.87</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>122.27</v>
+        <v>120.19</v>
       </c>
       <c r="G2">
-        <v>0.467</v>
+        <v>0.479</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2958,28 +3096,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>121.69</v>
+        <v>127.63</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>120.3</v>
+        <v>121.51</v>
       </c>
       <c r="G3">
-        <v>0.444</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2987,28 +3125,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>110.88</v>
+        <v>136.32</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>119.81</v>
+        <v>119.03</v>
       </c>
       <c r="G4">
-        <v>0.444</v>
+        <v>0.542</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3016,28 +3154,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>99.59999999999999</v>
+        <v>120.71</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>120.35</v>
+        <v>117.83</v>
       </c>
       <c r="G5">
-        <v>0.467</v>
+        <v>0.417</v>
       </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3045,28 +3183,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <v>95.28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>116.55</v>
+      </c>
+      <c r="G6">
+        <v>0.438</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6">
-        <v>128.1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>122.26</v>
-      </c>
-      <c r="G6">
-        <v>0.556</v>
-      </c>
-      <c r="H6">
-        <v>1.4</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3074,28 +3212,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>118.4</v>
+        <v>114.14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>119.66</v>
+        <v>116.14</v>
       </c>
       <c r="G7">
-        <v>0.489</v>
+        <v>0.417</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3103,28 +3241,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>116.65</v>
+        <v>110.75</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>118.92</v>
+        <v>118.24</v>
       </c>
       <c r="G8">
-        <v>0.511</v>
+        <v>0.583</v>
       </c>
       <c r="H8">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3132,28 +3270,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>145.5</v>
+        <v>114.15</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>117.51</v>
+        <v>116.96</v>
       </c>
       <c r="G9">
-        <v>0.511</v>
+        <v>0.542</v>
       </c>
       <c r="H9">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3161,28 +3299,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>111.15</v>
+        <v>127.19</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10">
-        <v>118.81</v>
+        <v>118.2</v>
       </c>
       <c r="G10">
-        <v>0.556</v>
+        <v>0.542</v>
       </c>
       <c r="H10">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3193,25 +3331,25 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>105.62</v>
+        <v>104.39</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11">
-        <v>117.16</v>
+        <v>116.8</v>
       </c>
       <c r="G11">
-        <v>0.489</v>
+        <v>0.521</v>
       </c>
       <c r="H11">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3219,28 +3357,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>124.97</v>
+        <v>115.8</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>116.9</v>
+        <v>116.39</v>
       </c>
       <c r="G12">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>-2.6</v>
+        <v>-2.1</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3248,28 +3386,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13">
-        <v>128.33</v>
+        <v>125.27</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>119.73</v>
+        <v>115.67</v>
       </c>
       <c r="G13">
-        <v>0.578</v>
+        <v>0.479</v>
       </c>
       <c r="H13">
-        <v>-3.2</v>
+        <v>-3.9</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3284,31 +3422,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3316,231 +3454,231 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>145.5</v>
+        <v>136.32</v>
       </c>
       <c r="E2">
-        <v>727.5</v>
+        <v>817.92</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>128.104</v>
+        <v>125.27</v>
       </c>
       <c r="E3">
-        <v>640.52</v>
+        <v>751.62</v>
       </c>
       <c r="F3">
-        <v>95.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4">
-        <v>124.968</v>
+        <v>121.87</v>
       </c>
       <c r="E4">
-        <v>624.84</v>
+        <v>731.22</v>
       </c>
       <c r="F4">
-        <v>89.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>122.8</v>
+        <v>127.6266666666667</v>
       </c>
       <c r="E5">
-        <v>614</v>
+        <v>765.76</v>
       </c>
       <c r="F5">
-        <v>89.60000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D6">
-        <v>118.404</v>
+        <v>114.14</v>
       </c>
       <c r="E6">
-        <v>592.02</v>
+        <v>684.8400000000001</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>110.876</v>
+        <v>114.1533333333333</v>
       </c>
       <c r="E7">
-        <v>554.3800000000001</v>
+        <v>684.92</v>
       </c>
       <c r="F7">
-        <v>68.89999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>121.692</v>
+        <v>127.1933333333333</v>
       </c>
       <c r="E8">
-        <v>608.4599999999999</v>
+        <v>763.16</v>
       </c>
       <c r="F8">
-        <v>58.3</v>
+        <v>66.60000000000001</v>
       </c>
       <c r="G8">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>128.328</v>
+        <v>120.71</v>
       </c>
       <c r="E9">
-        <v>641.64</v>
+        <v>724.2599999999999</v>
       </c>
       <c r="F9">
-        <v>56.2</v>
+        <v>43.6</v>
       </c>
       <c r="G9">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3548,28 +3686,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>116.648</v>
+        <v>115.7966666666666</v>
       </c>
       <c r="E10">
-        <v>583.2399999999999</v>
+        <v>694.7799999999999</v>
       </c>
       <c r="F10">
-        <v>42.7</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3577,86 +3715,86 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>111.148</v>
+        <v>110.7466666666667</v>
       </c>
       <c r="E11">
-        <v>555.7399999999999</v>
+        <v>664.4799999999999</v>
       </c>
       <c r="F11">
-        <v>9.700000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="G11">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D12">
-        <v>105.62</v>
+        <v>95.28333333333335</v>
       </c>
       <c r="E12">
-        <v>528.1</v>
+        <v>571.7</v>
       </c>
       <c r="F12">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>39.1</v>
+        <v>51.1</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>99.604</v>
+        <v>104.3933333333333</v>
       </c>
       <c r="E13">
-        <v>498.02</v>
+        <v>626.36</v>
       </c>
       <c r="F13">
-        <v>0.7000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>50.1</v>
+        <v>45.9</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3671,19 +3809,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3691,19 +3829,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3714,16 +3852,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3734,7 +3872,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -3743,7 +3881,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3751,19 +3889,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>54</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3771,19 +3909,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3791,19 +3929,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3811,19 +3949,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3831,19 +3969,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3851,19 +3989,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3871,19 +4009,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3891,19 +4029,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3914,16 +4052,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13">
-        <v>-17</v>
+        <v>-28</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3933,53 +4071,59 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>116</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3998,11 +4142,14 @@
       <c r="F3">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -4021,195 +4168,222 @@
       <c r="F4">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>11</v>
       </c>
       <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
         <v>-2</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>-4</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>-1</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>7</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>6</v>
       </c>
-      <c r="G6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>-1</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>-6</v>
+      </c>
+      <c r="G9">
+        <v>-3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>-1</v>
+      </c>
+      <c r="D10">
+        <v>-10</v>
+      </c>
+      <c r="E10">
+        <v>-8</v>
+      </c>
+      <c r="F10">
+        <v>-16</v>
+      </c>
+      <c r="G10">
+        <v>-6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>-8</v>
       </c>
-      <c r="F9">
+      <c r="F11">
         <v>-4</v>
       </c>
-      <c r="G9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>-6</v>
-      </c>
-      <c r="G10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
+      <c r="G11">
+        <v>-9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>-10</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>-10</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>-17</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>-17</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>-13</v>
       </c>
-      <c r="G11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>-1</v>
-      </c>
-      <c r="D12">
-        <v>-10</v>
-      </c>
-      <c r="E12">
-        <v>-8</v>
-      </c>
-      <c r="F12">
-        <v>-16</v>
-      </c>
-      <c r="G12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="G12">
+        <v>-15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -4228,8 +4402,11 @@
       <c r="F13">
         <v>-17</v>
       </c>
-      <c r="G13" t="s">
-        <v>101</v>
+      <c r="G13">
+        <v>-28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="125">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -61,25 +61,28 @@
     <t>Cman</t>
   </si>
   <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -160,6 +163,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -184,36 +190,36 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Shane Leiphart</t>
+  </si>
+  <si>
     <t>Robbie Wilston</t>
   </si>
   <si>
-    <t>Shane Leiphart</t>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Chris Holloway</t>
+  </si>
+  <si>
+    <t>Colman Closser</t>
   </si>
   <si>
     <t>Michael  Celoni</t>
   </si>
   <si>
-    <t>Chris Holloway</t>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
+    <t>Tomas Angel</t>
   </si>
   <si>
     <t>Joseph Wood</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Chris Carbone</t>
-  </si>
-  <si>
     <t>Eli Brinker</t>
   </si>
   <si>
-    <t>Tomas Angel</t>
-  </si>
-  <si>
-    <t>Colman Closser</t>
-  </si>
-  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
@@ -241,75 +247,78 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>10.5-3.5-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>6.3-7.6-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.7-0.1</t>
-  </si>
-  <si>
-    <t>2.9-11.0-0.1</t>
-  </si>
-  <si>
-    <t>2.6-11.3-0.1</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>0-7</t>
+  </si>
+  <si>
+    <t>10.6-3.4-0.1</t>
+  </si>
+  <si>
+    <t>9.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>2.0-11.9-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>3-11</t>
   </si>
   <si>
@@ -325,36 +334,27 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑7</t>
   </si>
   <si>
     <t>↓9</t>
   </si>
   <si>
-    <t>↑5</t>
+    <t>↑1</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑10</t>
+    <t>↓1</t>
   </si>
   <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↓2</t>
-  </si>
-  <si>
     <t>↓11</t>
   </si>
   <si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -801,34 +804,34 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" t="s">
         <v>14</v>
@@ -845,34 +848,34 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -883,34 +886,34 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" t="s">
         <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
       </c>
       <c r="M4" t="s">
         <v>14</v>
@@ -924,28 +927,28 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
@@ -962,13 +965,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -986,13 +989,13 @@
         <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
         <v>14</v>
@@ -1003,40 +1006,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="M7" t="s">
         <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1044,7 +1047,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1053,28 +1056,28 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -1085,19 +1088,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1106,19 +1109,19 @@
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1129,34 +1132,34 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
       </c>
       <c r="K10" t="s">
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
         <v>12</v>
@@ -1170,34 +1173,34 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
@@ -1211,7 +1214,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1220,25 +1223,25 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" t="s">
         <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
       </c>
       <c r="K12" t="s">
         <v>13</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" t="s">
         <v>14</v>
@@ -1249,37 +1252,37 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M13" t="s">
         <v>12</v>
@@ -1292,30 +1295,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1654,32 +1657,6 @@
       </c>
       <c r="H14" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15">
-        <v>11</v>
-      </c>
-      <c r="F15">
-        <v>7</v>
-      </c>
-      <c r="G15">
-        <v>4</v>
-      </c>
-      <c r="H15" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1694,13 +1671,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1708,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1.583333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1722,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>1.833333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1736,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>2.416666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1753,10 +1730,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1764,13 +1741,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2.75</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1778,13 +1755,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.75</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1792,13 +1769,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3.25</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1806,13 +1783,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>3.416666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1823,7 +1800,7 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>3.666666666666667</v>
+        <v>4.25</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -1837,10 +1814,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>3.833333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1851,10 +1828,10 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>3.833333333333333</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1865,7 +1842,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>4.166666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -1883,16 +1860,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1903,13 +1880,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.416666666666667</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="D2">
-        <v>-0.583333333333333</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1920,13 +1897,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>3.916666666666667</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.08333333333333348</v>
+        <v>-0.08333333333333304</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1937,13 +1914,13 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>3.833333333333333</v>
+        <v>4.75</v>
       </c>
       <c r="D4">
-        <v>-0.1666666666666665</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1954,13 +1931,13 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>3.583333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D5">
-        <v>-1.416666666666667</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1971,13 +1948,13 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>3.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>1.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1985,16 +1962,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>3.166666666666667</v>
+        <v>3.75</v>
       </c>
       <c r="D7">
-        <v>-1.833333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2002,16 +1979,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2022,10 +1999,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>2.916666666666667</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D9">
-        <v>-1.083333333333333</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -2039,10 +2016,10 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>0.8333333333333335</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -2056,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>2.083333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D11">
-        <v>0.08333333333333348</v>
+        <v>-0.25</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -2090,13 +2067,13 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>0.9166666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D13">
-        <v>-0.08333333333333337</v>
+        <v>0.25</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2111,46 +2088,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2158,25 +2135,25 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>60.6</v>
+        <v>55.6</v>
       </c>
       <c r="C2">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>12.7</v>
       </c>
       <c r="E2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="F2">
         <v>2.9</v>
       </c>
       <c r="G2">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
         <v>0.1</v>
@@ -2202,34 +2179,34 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>9.699999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="C3">
-        <v>21.7</v>
+        <v>32.3</v>
       </c>
       <c r="D3">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="F3">
-        <v>13.4</v>
+        <v>8.9</v>
       </c>
       <c r="G3">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2238,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>96.09999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2246,31 +2223,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="C4">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24.6</v>
       </c>
       <c r="E4">
-        <v>15.4</v>
+        <v>21.3</v>
       </c>
       <c r="F4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="G4">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
         <v>0.1</v>
@@ -2282,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>95.8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2290,34 +2267,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>8.300000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="C5">
-        <v>16.8</v>
+        <v>20.2</v>
       </c>
       <c r="D5">
-        <v>18.8</v>
+        <v>23.3</v>
       </c>
       <c r="E5">
-        <v>16.7</v>
+        <v>20.2</v>
       </c>
       <c r="F5">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G5">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J5">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2326,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>92.40000000000001</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2334,34 +2311,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="C6">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="D6">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="E6">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="F6">
-        <v>16.1</v>
+        <v>26.4</v>
       </c>
       <c r="G6">
-        <v>13.3</v>
+        <v>17.2</v>
       </c>
       <c r="H6">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2370,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>92.2</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2378,43 +2355,43 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="D7">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="E7">
-        <v>10.3</v>
+        <v>6.9</v>
       </c>
       <c r="F7">
-        <v>14.5</v>
+        <v>16.7</v>
       </c>
       <c r="G7">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="H7">
-        <v>16.8</v>
+        <v>19.5</v>
       </c>
       <c r="I7">
-        <v>13.2</v>
+        <v>16.3</v>
       </c>
       <c r="J7">
-        <v>8.4</v>
+        <v>11.9</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="L7">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>74.90000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2422,43 +2399,43 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="D8">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="E8">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="F8">
-        <v>13.3</v>
+        <v>10.8</v>
       </c>
       <c r="G8">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="H8">
-        <v>17.2</v>
+        <v>20.3</v>
       </c>
       <c r="I8">
-        <v>15.6</v>
+        <v>17.4</v>
       </c>
       <c r="J8">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="L8">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N8">
-        <v>66.59999999999999</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2469,128 +2446,128 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="F9">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="G9">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="H9">
-        <v>16.6</v>
+        <v>20.3</v>
       </c>
       <c r="I9">
         <v>22</v>
       </c>
       <c r="J9">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="K9">
-        <v>11.6</v>
+        <v>14.1</v>
       </c>
       <c r="L9">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="M9">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="N9">
-        <v>43.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0.7</v>
       </c>
       <c r="E10">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="F10">
         <v>3.4</v>
       </c>
       <c r="G10">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="H10">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="I10">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="J10">
-        <v>29.4</v>
+        <v>23.3</v>
       </c>
       <c r="K10">
-        <v>21</v>
+        <v>32.3</v>
       </c>
       <c r="L10">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="N10">
-        <v>26</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="H11">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="I11">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="J11">
-        <v>18.5</v>
+        <v>24.4</v>
       </c>
       <c r="K11">
-        <v>44.2</v>
+        <v>31.3</v>
       </c>
       <c r="L11">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="M11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2619,19 +2596,19 @@
         <v>0.2</v>
       </c>
       <c r="I12">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="K12">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
-        <v>38.7</v>
+        <v>54.7</v>
       </c>
       <c r="M12">
-        <v>51.1</v>
+        <v>37.8</v>
       </c>
       <c r="N12">
         <v>0.2</v>
@@ -2663,19 +2640,19 @@
         <v>0.1</v>
       </c>
       <c r="I13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J13">
+        <v>0.9</v>
+      </c>
+      <c r="K13">
         <v>2.2</v>
       </c>
-      <c r="K13">
-        <v>7.3</v>
-      </c>
       <c r="L13">
-        <v>44.2</v>
+        <v>35.1</v>
       </c>
       <c r="M13">
-        <v>45.9</v>
+        <v>61.7</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -2688,33 +2665,36 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2728,123 +2708,138 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2">
         <v>99.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>95.5</v>
+      </c>
+      <c r="C3">
+        <v>65.7</v>
+      </c>
+      <c r="D3">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>66.3</v>
+      </c>
+      <c r="F3">
+        <v>90.5</v>
+      </c>
+      <c r="G3">
+        <v>94.5</v>
+      </c>
+      <c r="H3">
+        <v>99.3</v>
+      </c>
+      <c r="I3">
+        <v>99.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>90.3</v>
-      </c>
-      <c r="C3">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D3">
-        <v>99.8</v>
-      </c>
-      <c r="E3">
+      <c r="B4">
+        <v>89.5</v>
+      </c>
+      <c r="C4">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D4">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E4">
         <v>100</v>
       </c>
-      <c r="F3">
-        <v>90.60000000000001</v>
-      </c>
-      <c r="G3">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="H3">
-        <v>95.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="C4">
-        <v>66.10000000000001</v>
-      </c>
-      <c r="D4">
-        <v>92.5</v>
-      </c>
-      <c r="E4">
-        <v>61.8</v>
-      </c>
       <c r="F4">
-        <v>90.7</v>
+        <v>91.5</v>
       </c>
       <c r="G4">
         <v>95.19999999999999</v>
       </c>
       <c r="H4">
-        <v>94.19999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I4">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>95.8</v>
+      </c>
+      <c r="E5">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F5">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G5">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I5">
+        <v>97.39999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>97.8</v>
-      </c>
-      <c r="C5">
-        <v>94.5</v>
-      </c>
-      <c r="D5">
-        <v>34.7</v>
-      </c>
-      <c r="E5">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="F5">
-        <v>65.3</v>
-      </c>
-      <c r="G5">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="H5">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B6">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D6">
-        <v>95.7</v>
+        <v>33.90000000000001</v>
       </c>
       <c r="E6">
-        <v>90.60000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="F6">
-        <v>96.7</v>
+        <v>68.2</v>
       </c>
       <c r="G6">
-        <v>93.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H6">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>84</v>
+      </c>
+      <c r="I6">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2852,177 +2847,198 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>37.5</v>
+        <v>38.9</v>
       </c>
       <c r="D7">
-        <v>23.3</v>
+        <v>21.5</v>
       </c>
       <c r="E7">
-        <v>64.5</v>
+        <v>65.2</v>
       </c>
       <c r="F7">
-        <v>85.7</v>
+        <v>86.8</v>
       </c>
       <c r="G7">
-        <v>68.30000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="H7">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>61.5</v>
+      </c>
+      <c r="I7">
+        <v>67.60000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="C8">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="D8">
-        <v>77.10000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="E8">
-        <v>83.89999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F8">
-        <v>62.8</v>
+        <v>60.09999999999999</v>
       </c>
       <c r="G8">
-        <v>70.19999999999999</v>
+        <v>69.69999999999999</v>
       </c>
       <c r="H8">
-        <v>67.10000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>59</v>
+      </c>
+      <c r="I8">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B9">
-        <v>22.3</v>
+        <v>20.2</v>
       </c>
       <c r="C9">
-        <v>90.10000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D9">
-        <v>95.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="E9">
-        <v>76.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F9">
-        <v>59.9</v>
+        <v>58.8</v>
       </c>
       <c r="G9">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="H9">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>37.4</v>
+      </c>
+      <c r="I9">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="C10">
-        <v>30.2</v>
+        <v>29.5</v>
       </c>
       <c r="D10">
-        <v>70.39999999999999</v>
+        <v>70.89999999999999</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="F10">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="G10">
-        <v>30.3</v>
+        <v>27.6</v>
       </c>
       <c r="H10">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>30.7</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
         <v>3.7</v>
       </c>
       <c r="E11">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="F11">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>17.6</v>
       </c>
       <c r="H11">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>32.2</v>
+      </c>
+      <c r="I11">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>39.1</v>
+        <v>44.2</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>13.4</v>
       </c>
       <c r="D12">
-        <v>7.399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E12">
         <v>0.6</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H12">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B13">
-        <v>41.3</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="C13">
-        <v>10.8</v>
+        <v>61.9</v>
       </c>
       <c r="D13">
+        <v>8.6</v>
+      </c>
+      <c r="E13">
         <v>0.3</v>
       </c>
-      <c r="E13">
-        <v>0.6</v>
-      </c>
       <c r="F13">
-        <v>0.8999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G13">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
     </row>
@@ -3038,28 +3054,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3070,25 +3086,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>121.87</v>
+        <v>121.16</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>120.19</v>
+        <v>119.52</v>
       </c>
       <c r="G2">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3096,28 +3112,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>127.63</v>
+        <v>133.1</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>121.51</v>
+        <v>118.75</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.51</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3125,28 +3141,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>136.32</v>
+        <v>128.25</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4">
-        <v>119.03</v>
+        <v>120.16</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.592</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3154,28 +3170,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>120.71</v>
+        <v>111.85</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>117.83</v>
+        <v>119.54</v>
       </c>
       <c r="G5">
-        <v>0.417</v>
+        <v>0.633</v>
       </c>
       <c r="H5">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3186,25 +3202,25 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>95.28</v>
+        <v>97.13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>116.55</v>
+        <v>115.35</v>
       </c>
       <c r="G6">
-        <v>0.438</v>
+        <v>0.429</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3212,28 +3228,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>114.14</v>
+        <v>110.29</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>116.14</v>
+        <v>117.66</v>
       </c>
       <c r="G7">
-        <v>0.417</v>
+        <v>0.571</v>
       </c>
       <c r="H7">
-        <v>-1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3241,28 +3257,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>110.75</v>
+        <v>121.27</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>118.24</v>
+        <v>115.07</v>
       </c>
       <c r="G8">
-        <v>0.583</v>
+        <v>0.408</v>
       </c>
       <c r="H8">
-        <v>-1.4</v>
+        <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3273,25 +3289,25 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>114.15</v>
+        <v>111.85</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9">
-        <v>116.96</v>
+        <v>115.39</v>
       </c>
       <c r="G9">
-        <v>0.542</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3299,28 +3315,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>127.19</v>
+        <v>100.28</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>118.2</v>
+        <v>116.45</v>
       </c>
       <c r="G10">
-        <v>0.542</v>
+        <v>0.51</v>
       </c>
       <c r="H10">
-        <v>-1.8</v>
+        <v>-2.7</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3328,28 +3344,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>104.39</v>
+        <v>110.88</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>116.8</v>
+        <v>112.04</v>
       </c>
       <c r="G11">
-        <v>0.521</v>
+        <v>0.367</v>
       </c>
       <c r="H11">
-        <v>-2.1</v>
+        <v>-3.4</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3357,28 +3373,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>115.8</v>
+        <v>126.59</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>116.39</v>
+        <v>116.01</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H12">
-        <v>-2.1</v>
+        <v>-3.6</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3389,25 +3405,25 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>125.27</v>
+        <v>126.26</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>115.67</v>
+        <v>112.97</v>
       </c>
       <c r="G13">
-        <v>0.479</v>
+        <v>0.469</v>
       </c>
       <c r="H13">
-        <v>-3.9</v>
+        <v>-6.7</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3422,31 +3438,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3454,16 +3470,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D2">
-        <v>136.32</v>
+        <v>133.1</v>
       </c>
       <c r="E2">
-        <v>817.92</v>
+        <v>931.6999999999999</v>
       </c>
       <c r="F2">
         <v>99.90000000000001</v>
@@ -3472,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3483,28 +3499,28 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>125.27</v>
+        <v>126.26</v>
       </c>
       <c r="E3">
-        <v>751.62</v>
+        <v>883.8199999999999</v>
       </c>
       <c r="F3">
-        <v>96.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3512,28 +3528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D4">
-        <v>121.87</v>
+        <v>121.16</v>
       </c>
       <c r="E4">
-        <v>731.22</v>
+        <v>848.12</v>
       </c>
       <c r="F4">
-        <v>95.8</v>
+        <v>99</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3541,28 +3557,28 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D5">
-        <v>127.6266666666667</v>
+        <v>128.2457142857143</v>
       </c>
       <c r="E5">
-        <v>765.76</v>
+        <v>897.72</v>
       </c>
       <c r="F5">
-        <v>92.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3570,28 +3586,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6">
-        <v>114.14</v>
+        <v>110.88</v>
       </c>
       <c r="E6">
-        <v>684.8400000000001</v>
+        <v>776.1600000000001</v>
       </c>
       <c r="F6">
-        <v>92.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3599,28 +3615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>114.1533333333333</v>
+        <v>111.8514285714286</v>
       </c>
       <c r="E7">
-        <v>684.92</v>
+        <v>782.9599999999999</v>
       </c>
       <c r="F7">
-        <v>74.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3628,28 +3644,28 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D8">
-        <v>127.1933333333333</v>
+        <v>126.5914285714286</v>
       </c>
       <c r="E8">
-        <v>763.16</v>
+        <v>886.14</v>
       </c>
       <c r="F8">
-        <v>66.60000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3657,86 +3673,86 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>120.71</v>
+        <v>121.2685714285714</v>
       </c>
       <c r="E9">
-        <v>724.2599999999999</v>
+        <v>848.8799999999999</v>
       </c>
       <c r="F9">
-        <v>43.6</v>
+        <v>41.09999999999999</v>
       </c>
       <c r="G9">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D10">
-        <v>115.7966666666666</v>
+        <v>111.8542857142857</v>
       </c>
       <c r="E10">
-        <v>694.7799999999999</v>
+        <v>782.9799999999999</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>23.7</v>
       </c>
       <c r="G10">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D11">
-        <v>110.7466666666667</v>
+        <v>110.2857142857143</v>
       </c>
       <c r="E11">
-        <v>664.4799999999999</v>
+        <v>771.9999999999999</v>
       </c>
       <c r="F11">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="G11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3744,28 +3760,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C12">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D12">
-        <v>95.28333333333335</v>
+        <v>97.12857142857145</v>
       </c>
       <c r="E12">
-        <v>571.7</v>
+        <v>679.9000000000001</v>
       </c>
       <c r="F12">
         <v>0.2</v>
       </c>
       <c r="G12">
-        <v>51.1</v>
+        <v>37.8</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3773,28 +3789,28 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>104.3933333333333</v>
+        <v>100.2828571428571</v>
       </c>
       <c r="E13">
-        <v>626.36</v>
+        <v>701.98</v>
       </c>
       <c r="F13">
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>45.9</v>
+        <v>61.7</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3809,19 +3825,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3832,16 +3848,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3849,19 +3865,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3869,19 +3885,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3889,19 +3905,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3909,19 +3925,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D6">
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3932,16 +3948,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3949,19 +3965,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3972,16 +3988,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3992,16 +4008,16 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4009,19 +4025,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4029,19 +4045,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4052,16 +4068,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4071,10 +4087,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>111</v>
       </c>
@@ -4094,10 +4110,13 @@
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>117</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4119,115 +4138,130 @@
       <c r="G2">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3">
+        <v>-4</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>11</v>
       </c>
-      <c r="B3">
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>-1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C6">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>-2</v>
-      </c>
-      <c r="C4">
-        <v>-4</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>13</v>
-      </c>
-      <c r="F4">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="H6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -4249,37 +4283,43 @@
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>-1</v>
-      </c>
-      <c r="C8">
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
         <v>4</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -4301,11 +4341,14 @@
       <c r="G9">
         <v>-3</v>
       </c>
-      <c r="H9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9">
+        <v>-4</v>
+      </c>
+      <c r="I9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4327,63 +4370,72 @@
       <c r="G10">
         <v>-6</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>-11</v>
+      </c>
+      <c r="I10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>-10</v>
+      </c>
+      <c r="C11">
+        <v>-10</v>
+      </c>
+      <c r="D11">
+        <v>-17</v>
+      </c>
+      <c r="E11">
+        <v>-17</v>
+      </c>
+      <c r="F11">
+        <v>-13</v>
+      </c>
+      <c r="G11">
+        <v>-15</v>
+      </c>
+      <c r="H11">
+        <v>-18</v>
+      </c>
+      <c r="I11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>-8</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>-4</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>-9</v>
       </c>
-      <c r="H11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>-10</v>
-      </c>
-      <c r="C12">
-        <v>-10</v>
-      </c>
-      <c r="D12">
-        <v>-17</v>
-      </c>
-      <c r="E12">
-        <v>-17</v>
-      </c>
-      <c r="F12">
-        <v>-13</v>
-      </c>
-      <c r="G12">
-        <v>-15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12">
+        <v>-20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -4405,8 +4457,11 @@
       <c r="G13">
         <v>-28</v>
       </c>
-      <c r="H13" t="s">
-        <v>110</v>
+      <c r="H13">
+        <v>-29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Pennoni Younglings 2026.xlsx
+++ b/data/leagues/Pennoni Younglings 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="124">
   <si>
     <t>Daddy's Finally Home</t>
   </si>
@@ -268,16 +268,13 @@
     <t>0-7</t>
   </si>
   <si>
-    <t>10.6-3.4-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
+    <t>10.7-3.3-0.1</t>
   </si>
   <si>
     <t>9.6-4.3-0.1</t>
   </si>
   <si>
-    <t>9.2-4.7-0.1</t>
+    <t>9.2-4.8-0.1</t>
   </si>
   <si>
     <t>8.4-5.5-0.1</t>
@@ -292,13 +289,10 @@
     <t>6.0-7.9-0.1</t>
   </si>
   <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
     <t>5.8-8.1-0.1</t>
   </si>
   <si>
-    <t>2.8-11.1-0.1</t>
+    <t>2.9-11.1-0.1</t>
   </si>
   <si>
     <t>2.0-11.9-0.1</t>
@@ -307,10 +301,13 @@
     <t>11-3</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
@@ -1300,25 +1297,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2135,31 +2132,31 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>55.6</v>
+        <v>58.8</v>
       </c>
       <c r="C2">
-        <v>19.7</v>
+        <v>22.6</v>
       </c>
       <c r="D2">
-        <v>12.7</v>
+        <v>10.3</v>
       </c>
       <c r="E2">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="F2">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0.1</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2176,31 +2173,31 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="C3">
-        <v>32.3</v>
+        <v>21.3</v>
       </c>
       <c r="D3">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
       <c r="E3">
-        <v>17.8</v>
+        <v>21.9</v>
       </c>
       <c r="F3">
-        <v>8.9</v>
+        <v>12.5</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2215,42 +2212,42 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>19.7</v>
+        <v>27.9</v>
       </c>
       <c r="D4">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>21.3</v>
+        <v>17.2</v>
       </c>
       <c r="F4">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="G4">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2259,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2267,34 +2264,34 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>13.3</v>
+        <v>11.7</v>
       </c>
       <c r="C5">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="D5">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="E5">
-        <v>20.2</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="I5">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2303,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2311,34 +2308,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="C6">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="D6">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="E6">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="F6">
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="G6">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2347,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>89.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2355,34 +2352,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="D7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E7">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="G7">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="H7">
-        <v>19.5</v>
+        <v>20.4</v>
       </c>
       <c r="I7">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="J7">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="K7">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="L7">
         <v>0.6</v>
@@ -2391,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>65.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2402,40 +2399,40 @@
         <v>0.1</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="E8">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="F8">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G8">
-        <v>21.3</v>
+        <v>18.9</v>
       </c>
       <c r="H8">
-        <v>20.3</v>
+        <v>19.2</v>
       </c>
       <c r="I8">
-        <v>17.4</v>
+        <v>22.3</v>
       </c>
       <c r="J8">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="K8">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
-        <v>59.8</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2446,40 +2443,40 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D9">
         <v>0.2</v>
       </c>
       <c r="E9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>5.7</v>
       </c>
       <c r="G9">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="H9">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="J9">
-        <v>19.8</v>
+        <v>23.3</v>
       </c>
       <c r="K9">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="L9">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="M9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>41.1</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2493,37 +2490,37 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F10">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="G10">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="I10">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="J10">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="K10">
-        <v>32.3</v>
+        <v>31.1</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M10">
         <v>0.2</v>
       </c>
       <c r="N10">
-        <v>23.7</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2531,43 +2528,43 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F11">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H11">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="I11">
-        <v>17.7</v>
+        <v>19</v>
       </c>
       <c r="J11">
-        <v>24.4</v>
+        <v>22</v>
       </c>
       <c r="K11">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="L11">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N11">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2590,25 +2587,25 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>54.7</v>
+        <v>56.1</v>
       </c>
       <c r="M12">
-        <v>37.8</v>
+        <v>36.5</v>
       </c>
       <c r="N12">
         <v>0.2</v>
@@ -2643,16 +2640,16 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K13">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>35.1</v>
+        <v>34.7</v>
       </c>
       <c r="M13">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -2717,10 +2714,10 @@
         <v>99.59999999999999</v>
       </c>
       <c r="H2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2746,10 +2743,10 @@
         <v>94.5</v>
       </c>
       <c r="H3">
-        <v>99.3</v>
+        <v>98.7</v>
       </c>
       <c r="I3">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2775,10 +2772,10 @@
         <v>95.19999999999999</v>
       </c>
       <c r="H4">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I4">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2804,10 +2801,10 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I5">
-        <v>97.39999999999999</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2833,10 +2830,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="H6">
-        <v>84</v>
+        <v>83.39999999999999</v>
       </c>
       <c r="I6">
-        <v>88.3</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2862,10 +2859,10 @@
         <v>71.3</v>
       </c>
       <c r="H7">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
       <c r="I7">
-        <v>67.60000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2891,10 +2888,10 @@
         <v>69.69999999999999</v>
       </c>
       <c r="H8">
-        <v>59</v>
+        <v>55.2</v>
       </c>
       <c r="I8">
-        <v>61.5</v>
+        <v>60.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2920,10 +2917,10 @@
         <v>43.6</v>
       </c>
       <c r="H9">
-        <v>37.4</v>
+        <v>38.5</v>
       </c>
       <c r="I9">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2949,10 +2946,10 @@
         <v>27.6</v>
       </c>
       <c r="H10">
-        <v>30.7</v>
+        <v>29.9</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2978,10 +2975,10 @@
         <v>17.6</v>
       </c>
       <c r="H11">
-        <v>32.2</v>
+        <v>35.6</v>
       </c>
       <c r="I11">
-        <v>23.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3007,7 +3004,7 @@
         <v>0.2</v>
       </c>
       <c r="H12">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I12">
         <v>0.2</v>
@@ -3036,10 +3033,10 @@
         <v>0.3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3491,27 +3488,27 @@
         <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D3">
-        <v>126.26</v>
+        <v>121.16</v>
       </c>
       <c r="E3">
-        <v>883.8199999999999</v>
+        <v>848.12</v>
       </c>
       <c r="F3">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3520,36 +3517,36 @@
         <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>121.16</v>
+        <v>126.26</v>
       </c>
       <c r="E4">
-        <v>848.12</v>
+        <v>883.8199999999999</v>
       </c>
       <c r="F4">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3569,16 +3566,16 @@
         <v>897.72</v>
       </c>
       <c r="F5">
-        <v>98</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3598,16 +3595,16 @@
         <v>776.1600000000001</v>
       </c>
       <c r="F6">
-        <v>89.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3627,16 +3624,16 @@
         <v>782.9599999999999</v>
       </c>
       <c r="F7">
-        <v>65.8</v>
+        <v>66.8</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3656,13 +3653,13 @@
         <v>886.14</v>
       </c>
       <c r="F8">
-        <v>59.8</v>
+        <v>55.50000000000001</v>
       </c>
       <c r="G8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
         <v>96</v>
@@ -3685,16 +3682,16 @@
         <v>848.8799999999999</v>
       </c>
       <c r="F9">
-        <v>41.09999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3714,16 +3711,16 @@
         <v>782.9799999999999</v>
       </c>
       <c r="F10">
-        <v>23.7</v>
+        <v>27.2</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3743,16 +3740,16 @@
         <v>771.9999999999999</v>
       </c>
       <c r="F11">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3775,13 +3772,13 @@
         <v>0.2</v>
       </c>
       <c r="G12">
-        <v>37.8</v>
+        <v>36.5</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3804,13 +3801,13 @@
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3828,16 +3825,16 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3857,7 +3854,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3877,7 +3874,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3897,7 +3894,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3917,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3937,7 +3934,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3957,7 +3954,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3977,7 +3974,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3997,7 +3994,7 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4017,7 +4014,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4037,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4057,7 +4054,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4077,7 +4074,7 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -4092,28 +4089,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4142,7 +4139,7 @@
         <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4171,7 +4168,7 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4200,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4229,7 +4226,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4258,7 +4255,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4287,7 +4284,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -4316,7 +4313,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4345,7 +4342,7 @@
         <v>-4</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4374,7 +4371,7 @@
         <v>-11</v>
       </c>
       <c r="I10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4403,7 +4400,7 @@
         <v>-18</v>
       </c>
       <c r="I11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4432,7 +4429,7 @@
         <v>-20</v>
       </c>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4461,7 +4458,7 @@
         <v>-29</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
